--- a/data/source/weekly/cs-en-us-041pct.xlsx
+++ b/data/source/weekly/cs-en-us-041pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -896,31 +896,31 @@
         <v>20</v>
       </c>
       <c r="D15" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="14">
         <v>-100</v>
       </c>
       <c r="F15" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" s="14">
-        <v>-33.333333333333</v>
+        <v>-75</v>
       </c>
       <c r="I15" s="15">
         <v>4</v>
       </c>
       <c r="J15" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="14">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L15" s="14">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="M15" s="14">
         <v>300</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" s="14">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="F16" s="15">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G16" s="15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H16" s="14">
-        <v>33.333333333333</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I16" s="15">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J16" s="15">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K16" s="14">
-        <v>21.052631578947</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L16" s="14">
-        <v>-28.125</v>
+        <v>-25.714285714285</v>
       </c>
       <c r="M16" s="14">
-        <v>-14.814814814814</v>
+        <v>-10.344827586206</v>
       </c>
       <c r="N16" s="14">
-        <v>-70.512820512820</v>
+        <v>-72.340425531914</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D17" s="15">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E17" s="14">
-        <v>14.285714285714</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F17" s="15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G17" s="15">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H17" s="14">
-        <v>-26.470588235294</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="I17" s="15">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="J17" s="15">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="K17" s="14">
-        <v>-38.775510204081</v>
+        <v>-36.666666666666</v>
       </c>
       <c r="L17" s="14">
-        <v>-38.775510204081</v>
+        <v>-35.593220338983</v>
       </c>
       <c r="M17" s="14">
-        <v>-28.571428571428</v>
+        <v>-19.148936170212</v>
       </c>
       <c r="N17" s="14">
-        <v>-9.090909090909</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E18" s="14">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="F18" s="15">
         <v>9</v>
       </c>
       <c r="G18" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H18" s="14">
-        <v>-40</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="I18" s="15">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J18" s="15">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K18" s="14">
-        <v>-22.222222222222</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="L18" s="14">
-        <v>-22.222222222222</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="M18" s="14">
-        <v>-26.315789473684</v>
+        <v>-32</v>
       </c>
       <c r="N18" s="14">
-        <v>-82.278481012658</v>
+        <v>-82.653061224489</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D19" s="15">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E19" s="14">
-        <v>-50</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F19" s="15">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G19" s="15">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H19" s="14">
-        <v>-26.470588235294</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="I19" s="15">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="J19" s="15">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K19" s="14">
-        <v>-23.809523809523</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L19" s="14">
-        <v>-21.951219512195</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M19" s="14">
-        <v>18.518518518518</v>
+        <v>21.212121212121</v>
       </c>
       <c r="N19" s="14">
-        <v>-17.948717948717</v>
+        <v>-11.111111111111</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>1</v>
       </c>
       <c r="D20" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F20" s="15">
         <v>2</v>
       </c>
       <c r="G20" s="15">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H20" s="14">
-        <v>-81.818181818181</v>
+        <v>-75</v>
       </c>
       <c r="I20" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J20" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K20" s="14">
-        <v>-76.470588235294</v>
+        <v>-72.222222222222</v>
       </c>
       <c r="L20" s="14">
-        <v>-80</v>
+        <v>-78.260869565217</v>
       </c>
       <c r="M20" s="14">
-        <v>-55.555555555555</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="N20" s="14">
-        <v>-88.888888888888</v>
+        <v>-88.372093023255</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D21" s="17">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E21" s="18">
-        <v>-31.034482758620</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="F21" s="17">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G21" s="17">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H21" s="18">
-        <v>-25.892857142857</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="I21" s="17">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="J21" s="17">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="K21" s="18">
-        <v>-27.702702702702</v>
+        <v>-25.287356321839</v>
       </c>
       <c r="L21" s="18">
-        <v>-35.151515151515</v>
+        <v>-30.481283422459</v>
       </c>
       <c r="M21" s="18">
-        <v>-14.4</v>
+        <v>-10.958904109589</v>
       </c>
       <c r="N21" s="18">
-        <v>-60.805860805860</v>
+        <v>-60.365853658536</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1188,14 +1188,14 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="15">
-        <v>1</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="15">
         <v>1</v>
       </c>
       <c r="H22" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="15">
         <v>1</v>
@@ -1207,7 +1207,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L22" s="14">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="M22" s="14">
         <v>-66.666666666666</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="15">
+        <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1229,29 +1229,29 @@
       <c r="E23" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="13" t="s">
-        <v>20</v>
+      <c r="F23" s="15">
+        <v>1</v>
       </c>
       <c r="G23" s="15">
         <v>1</v>
       </c>
       <c r="H23" s="14">
-        <v>-100</v>
-      </c>
-      <c r="I23" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I23" s="15">
+        <v>1</v>
       </c>
       <c r="J23" s="15">
         <v>1</v>
       </c>
       <c r="K23" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L23" s="14">
-        <v>-100</v>
+        <v>-80</v>
       </c>
       <c r="M23" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,34 +1265,34 @@
         <v>13</v>
       </c>
       <c r="D24" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E24" s="14">
-        <v>-27.777777777777</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="F24" s="15">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G24" s="15">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H24" s="14">
-        <v>-33.333333333333</v>
+        <v>-40.277777777777</v>
       </c>
       <c r="I24" s="15">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="J24" s="15">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="K24" s="14">
-        <v>-31.764705882352</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="L24" s="14">
-        <v>-23.684210526315</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="M24" s="14">
-        <v>11.538461538461</v>
+        <v>24.137931034482</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D25" s="15">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E25" s="14">
-        <v>66.666666666666</v>
+        <v>-87.5</v>
       </c>
       <c r="F25" s="15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G25" s="15">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H25" s="14">
-        <v>-45.454545454545</v>
+        <v>-57.692307692307</v>
       </c>
       <c r="I25" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J25" s="15">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="K25" s="14">
-        <v>-44.444444444444</v>
+        <v>-54.285714285714</v>
       </c>
       <c r="L25" s="14">
-        <v>-31.818181818181</v>
+        <v>-36</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D26" s="15">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E26" s="14">
+        <v>-40</v>
+      </c>
+      <c r="F26" s="15">
+        <v>49</v>
+      </c>
+      <c r="G26" s="15">
+        <v>49</v>
+      </c>
+      <c r="H26" s="14">
         <v>0</v>
       </c>
-      <c r="F26" s="15">
-        <v>58</v>
-      </c>
-      <c r="G26" s="15">
-        <v>43</v>
-      </c>
-      <c r="H26" s="14">
-        <v>34.883720930232</v>
-      </c>
       <c r="I26" s="15">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="J26" s="15">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="K26" s="14">
-        <v>32.142857142857</v>
+        <v>11.842105263157</v>
       </c>
       <c r="L26" s="14">
-        <v>1.369863013698</v>
+        <v>3.658536585365</v>
       </c>
       <c r="M26" s="14">
-        <v>34.545454545454</v>
+        <v>39.344262295082</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>-100</v>
       </c>
       <c r="F27" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H27" s="14">
-        <v>-50</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="I27" s="15">
         <v>4</v>
       </c>
       <c r="J27" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K27" s="14">
-        <v>-33.333333333333</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L27" s="14">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1438,7 +1438,7 @@
         <v>20</v>
       </c>
       <c r="G28" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H28" s="14">
         <v>-100</v>
@@ -1447,13 +1447,13 @@
         <v>1</v>
       </c>
       <c r="J28" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K28" s="14">
-        <v>-88.888888888888</v>
+        <v>-90</v>
       </c>
       <c r="L28" s="14">
-        <v>-90</v>
+        <v>-90.909090909090</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-041pct.xlsx
+++ b/data/source/weekly/cs-en-us-041pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F15" s="15">
         <v>1</v>
       </c>
       <c r="G15" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H15" s="14">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="I15" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K15" s="14">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L15" s="14">
-        <v>-20</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M15" s="14">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="N15" s="14">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" s="15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>-40</v>
+        <v>100</v>
       </c>
       <c r="F16" s="15">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G16" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H16" s="14">
-        <v>28.571428571428</v>
+        <v>0</v>
       </c>
       <c r="I16" s="15">
+        <v>30</v>
+      </c>
+      <c r="J16" s="15">
         <v>26</v>
       </c>
-      <c r="J16" s="15">
-        <v>24</v>
-      </c>
       <c r="K16" s="14">
-        <v>8.333333333333</v>
+        <v>15.384615384615</v>
       </c>
       <c r="L16" s="14">
-        <v>-25.714285714285</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="M16" s="14">
-        <v>-10.344827586206</v>
+        <v>-3.225806451612</v>
       </c>
       <c r="N16" s="14">
-        <v>-72.340425531914</v>
+        <v>-71.153846153846</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D17" s="15">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E17" s="14">
-        <v>-36.363636363636</v>
+        <v>150</v>
       </c>
       <c r="F17" s="15">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G17" s="15">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H17" s="14">
-        <v>-27.777777777777</v>
+        <v>-8</v>
       </c>
       <c r="I17" s="15">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J17" s="15">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K17" s="14">
-        <v>-36.666666666666</v>
+        <v>-29.032258064516</v>
       </c>
       <c r="L17" s="14">
-        <v>-35.593220338983</v>
+        <v>-29.032258064516</v>
       </c>
       <c r="M17" s="14">
-        <v>-19.148936170212</v>
+        <v>-27.868852459016</v>
       </c>
       <c r="N17" s="14">
-        <v>-5</v>
+        <v>-4.347826086956</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D18" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E18" s="14">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="F18" s="15">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G18" s="15">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H18" s="14">
-        <v>-47.058823529411</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="I18" s="15">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J18" s="15">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="K18" s="14">
-        <v>-26.086956521739</v>
+        <v>-20</v>
       </c>
       <c r="L18" s="14">
-        <v>-10.526315789473</v>
+        <v>4.347826086956</v>
       </c>
       <c r="M18" s="14">
-        <v>-32</v>
+        <v>-20</v>
       </c>
       <c r="N18" s="14">
-        <v>-82.653061224489</v>
+        <v>-77.777777777777</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D19" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" s="14">
-        <v>166.666666666667</v>
+        <v>50</v>
       </c>
       <c r="F19" s="15">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G19" s="15">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H19" s="14">
-        <v>-24.137931034482</v>
+        <v>-5</v>
       </c>
       <c r="I19" s="15">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J19" s="15">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K19" s="14">
-        <v>-11.111111111111</v>
+        <v>-8.510638297872</v>
       </c>
       <c r="L19" s="14">
-        <v>-11.111111111111</v>
+        <v>-15.686274509803</v>
       </c>
       <c r="M19" s="14">
-        <v>21.212121212121</v>
+        <v>16.216216216216</v>
       </c>
       <c r="N19" s="14">
-        <v>-11.111111111111</v>
+        <v>-10.416666666666</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>1</v>
       </c>
       <c r="D20" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E20" s="14">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="F20" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="15">
         <v>8</v>
       </c>
       <c r="H20" s="14">
+        <v>-62.5</v>
+      </c>
+      <c r="I20" s="15">
+        <v>6</v>
+      </c>
+      <c r="J20" s="15">
+        <v>22</v>
+      </c>
+      <c r="K20" s="14">
+        <v>-72.727272727272</v>
+      </c>
+      <c r="L20" s="14">
         <v>-75</v>
       </c>
-      <c r="I20" s="15">
-        <v>5</v>
-      </c>
-      <c r="J20" s="15">
-        <v>18</v>
-      </c>
-      <c r="K20" s="14">
-        <v>-72.222222222222</v>
-      </c>
-      <c r="L20" s="14">
-        <v>-78.260869565217</v>
-      </c>
       <c r="M20" s="14">
-        <v>-54.545454545454</v>
+        <v>-50</v>
       </c>
       <c r="N20" s="14">
-        <v>-88.372093023255</v>
+        <v>-88.679245283018</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>-15.384615384615</v>
+        <v>10.526315789473</v>
       </c>
       <c r="F21" s="17">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G21" s="17">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="H21" s="18">
-        <v>-27.777777777777</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="I21" s="17">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="J21" s="17">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="K21" s="18">
-        <v>-25.287356321839</v>
+        <v>-21.243523316062</v>
       </c>
       <c r="L21" s="18">
-        <v>-30.481283422459</v>
+        <v>-25.853658536585</v>
       </c>
       <c r="M21" s="18">
-        <v>-10.958904109589</v>
+        <v>-11.627906976744</v>
       </c>
       <c r="N21" s="18">
-        <v>-60.365853658536</v>
+        <v>-58.695652173913</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="15">
+        <v>2</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1188,29 +1188,29 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+      <c r="F22" s="15">
+        <v>2</v>
       </c>
       <c r="G22" s="15">
         <v>1</v>
       </c>
       <c r="H22" s="14">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="I22" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J22" s="15">
         <v>3</v>
       </c>
       <c r="K22" s="14">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="L22" s="14">
-        <v>-75</v>
+        <v>-25</v>
       </c>
       <c r="M22" s="14">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1232,11 +1232,11 @@
       <c r="F23" s="15">
         <v>1</v>
       </c>
-      <c r="G23" s="15">
-        <v>1</v>
-      </c>
-      <c r="H23" s="14">
-        <v>0</v>
+      <c r="G23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I23" s="15">
         <v>1</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D24" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E24" s="14">
-        <v>-31.578947368421</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F24" s="15">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G24" s="15">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="H24" s="14">
-        <v>-40.277777777777</v>
+        <v>-38.271604938271</v>
       </c>
       <c r="I24" s="15">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="J24" s="15">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="K24" s="14">
-        <v>-30.769230769230</v>
+        <v>-30.4</v>
       </c>
       <c r="L24" s="14">
-        <v>-18.181818181818</v>
+        <v>-17.924528301886</v>
       </c>
       <c r="M24" s="14">
-        <v>24.137931034482</v>
+        <v>27.941176470588</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D25" s="15">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E25" s="14">
-        <v>-87.5</v>
+        <v>100</v>
       </c>
       <c r="F25" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G25" s="15">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H25" s="14">
-        <v>-57.692307692307</v>
+        <v>-44</v>
       </c>
       <c r="I25" s="15">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J25" s="15">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K25" s="14">
-        <v>-54.285714285714</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="L25" s="14">
-        <v>-36</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D26" s="15">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E26" s="14">
-        <v>-40</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="F26" s="15">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="G26" s="15">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H26" s="14">
-        <v>0</v>
+        <v>-28.301886792452</v>
       </c>
       <c r="I26" s="15">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="J26" s="15">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="K26" s="14">
-        <v>11.842105263157</v>
+        <v>3.370786516853</v>
       </c>
       <c r="L26" s="14">
-        <v>3.658536585365</v>
+        <v>-1.075268817204</v>
       </c>
       <c r="M26" s="14">
-        <v>39.344262295082</v>
+        <v>29.577464788732</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
       </c>
       <c r="D27" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F27" s="15">
         <v>1</v>
       </c>
       <c r="G27" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H27" s="14">
-        <v>-85.714285714285</v>
+        <v>-87.5</v>
       </c>
       <c r="I27" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J27" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K27" s="14">
-        <v>-55.555555555555</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="L27" s="14">
-        <v>-55.555555555555</v>
+        <v>-50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,17 +1428,17 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G28" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28" s="14">
         <v>-100</v>
@@ -1453,7 +1453,7 @@
         <v>-90</v>
       </c>
       <c r="L28" s="14">
-        <v>-90.909090909090</v>
+        <v>-92.857142857142</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-041pct.xlsx
+++ b/data/source/weekly/cs-en-us-041pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -896,37 +896,37 @@
         <v>1</v>
       </c>
       <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>0</v>
+      </c>
+      <c r="F15" s="15">
         <v>2</v>
       </c>
-      <c r="E15" s="14">
-        <v>-50</v>
-      </c>
-      <c r="F15" s="15">
-        <v>1</v>
-      </c>
       <c r="G15" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H15" s="14">
-        <v>-80</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I15" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J15" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K15" s="14">
-        <v>-16.666666666666</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L15" s="14">
-        <v>-16.666666666666</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M15" s="14">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="N15" s="14">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" s="15">
         <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G16" s="15">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H16" s="14">
         <v>0</v>
       </c>
       <c r="I16" s="15">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J16" s="15">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K16" s="14">
-        <v>15.384615384615</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L16" s="14">
-        <v>-21.052631578947</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="M16" s="14">
-        <v>-3.225806451612</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N16" s="14">
-        <v>-71.153846153846</v>
+        <v>-73.109243697479</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D17" s="15">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E17" s="14">
-        <v>150</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="F17" s="15">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G17" s="15">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H17" s="14">
-        <v>-8</v>
+        <v>-20</v>
       </c>
       <c r="I17" s="15">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J17" s="15">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="K17" s="14">
-        <v>-29.032258064516</v>
+        <v>-32.467532467532</v>
       </c>
       <c r="L17" s="14">
-        <v>-29.032258064516</v>
+        <v>-29.729729729729</v>
       </c>
       <c r="M17" s="14">
-        <v>-27.868852459016</v>
+        <v>-21.212121212121</v>
       </c>
       <c r="N17" s="14">
-        <v>-4.347826086956</v>
+        <v>-1.886792452830</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,13 +1016,13 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D18" s="15">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="15">
         <v>13</v>
@@ -1034,22 +1034,22 @@
         <v>-31.578947368421</v>
       </c>
       <c r="I18" s="15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J18" s="15">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K18" s="14">
-        <v>-20</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="L18" s="14">
-        <v>4.347826086956</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="M18" s="14">
-        <v>-20</v>
+        <v>-21.875</v>
       </c>
       <c r="N18" s="14">
-        <v>-77.777777777777</v>
+        <v>-79.838709677419</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E19" s="14">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="F19" s="15">
+        <v>18</v>
+      </c>
+      <c r="G19" s="15">
         <v>19</v>
       </c>
-      <c r="G19" s="15">
-        <v>20</v>
-      </c>
       <c r="H19" s="14">
-        <v>-5</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="I19" s="15">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J19" s="15">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="K19" s="14">
-        <v>-8.510638297872</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="L19" s="14">
-        <v>-15.686274509803</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M19" s="14">
-        <v>16.216216216216</v>
+        <v>0</v>
       </c>
       <c r="N19" s="14">
-        <v>-10.416666666666</v>
+        <v>-21.052631578947</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="15">
         <v>4</v>
       </c>
       <c r="E20" s="14">
-        <v>-75</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="15">
         <v>3</v>
       </c>
       <c r="G20" s="15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H20" s="14">
-        <v>-62.5</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="I20" s="15">
         <v>6</v>
       </c>
       <c r="J20" s="15">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K20" s="14">
-        <v>-72.727272727272</v>
+        <v>-76.923076923076</v>
       </c>
       <c r="L20" s="14">
-        <v>-75</v>
+        <v>-78.571428571428</v>
       </c>
       <c r="M20" s="14">
-        <v>-50</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="N20" s="14">
-        <v>-88.679245283018</v>
+        <v>-90.322580645161</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D21" s="17">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18">
-        <v>10.526315789473</v>
+        <v>-55.172413793103</v>
       </c>
       <c r="F21" s="17">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G21" s="17">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="H21" s="18">
-        <v>-19.354838709677</v>
+        <v>-25.242718446601</v>
       </c>
       <c r="I21" s="17">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="J21" s="17">
-        <v>193</v>
+        <v>222</v>
       </c>
       <c r="K21" s="18">
-        <v>-21.243523316062</v>
+        <v>-25.225225225225</v>
       </c>
       <c r="L21" s="18">
-        <v>-25.853658536585</v>
+        <v>-31.967213114754</v>
       </c>
       <c r="M21" s="18">
-        <v>-11.627906976744</v>
+        <v>-13.989637305699</v>
       </c>
       <c r="N21" s="18">
-        <v>-58.695652173913</v>
+        <v>-60.941176470588</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,7 +1180,7 @@
         <v>29</v>
       </c>
       <c r="C22" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,28 +1189,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>2</v>
-      </c>
-      <c r="G22" s="15">
-        <v>1</v>
-      </c>
-      <c r="H22" s="14">
-        <v>100</v>
+        <v>3</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J22" s="15">
         <v>3</v>
       </c>
       <c r="K22" s="14">
+        <v>33.333333333333</v>
+      </c>
+      <c r="L22" s="14">
         <v>0</v>
       </c>
-      <c r="L22" s="14">
-        <v>-25</v>
-      </c>
       <c r="M22" s="14">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1248,7 +1248,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="14">
-        <v>-80</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="M23" s="14">
         <v>0</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D24" s="15">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E24" s="14">
-        <v>-28.571428571428</v>
+        <v>-50</v>
       </c>
       <c r="F24" s="15">
         <v>50</v>
       </c>
       <c r="G24" s="15">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H24" s="14">
-        <v>-38.271604938271</v>
+        <v>-32.432432432432</v>
       </c>
       <c r="I24" s="15">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="J24" s="15">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="K24" s="14">
-        <v>-30.4</v>
+        <v>-32.624113475177</v>
       </c>
       <c r="L24" s="14">
-        <v>-17.924528301886</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="M24" s="14">
-        <v>27.941176470588</v>
+        <v>28.378378378378</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D25" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F25" s="15">
         <v>14</v>
       </c>
       <c r="G25" s="15">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H25" s="14">
-        <v>-44</v>
+        <v>-12.5</v>
       </c>
       <c r="I25" s="15">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J25" s="15">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K25" s="14">
-        <v>-42.105263157894</v>
+        <v>-40</v>
       </c>
       <c r="L25" s="14">
-        <v>-24.137931034482</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D26" s="15">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E26" s="14">
-        <v>-46.153846153846</v>
+        <v>12.5</v>
       </c>
       <c r="F26" s="15">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G26" s="15">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H26" s="14">
-        <v>-28.301886792452</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I26" s="15">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="J26" s="15">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="K26" s="14">
-        <v>3.370786516853</v>
+        <v>3.092783505154</v>
       </c>
       <c r="L26" s="14">
-        <v>-1.075268817204</v>
+        <v>-6.542056074766</v>
       </c>
       <c r="M26" s="14">
-        <v>29.577464788732</v>
+        <v>14.942528735632</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,22 +1394,22 @@
         <v>-50</v>
       </c>
       <c r="F27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H27" s="14">
-        <v>-87.5</v>
+        <v>-80</v>
       </c>
       <c r="I27" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J27" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K27" s="14">
-        <v>-54.545454545454</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="L27" s="14">
         <v>-50</v>
@@ -1428,17 +1428,17 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="15">
+        <v>4</v>
+      </c>
+      <c r="E28" s="14">
+        <v>-100</v>
       </c>
       <c r="F28" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G28" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H28" s="14">
         <v>-100</v>
@@ -1447,13 +1447,13 @@
         <v>1</v>
       </c>
       <c r="J28" s="15">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K28" s="14">
-        <v>-90</v>
+        <v>-92.857142857142</v>
       </c>
       <c r="L28" s="14">
-        <v>-92.857142857142</v>
+        <v>-93.75</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="15">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="15">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1484,8 +1484,8 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+      <c r="I29" s="15">
+        <v>1</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>20</v>
@@ -1494,21 +1494,21 @@
         <v>21</v>
       </c>
       <c r="L29" s="14">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="M29" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N29" s="14">
-        <v>-100</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="15">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="15">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1525,8 +1525,8 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+      <c r="I30" s="15">
+        <v>1</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>20</v>
@@ -1535,13 +1535,13 @@
         <v>21</v>
       </c>
       <c r="L30" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M30" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N30" s="14">
-        <v>-100</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-041pct.xlsx
+++ b/data/source/weekly/cs-en-us-041pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -895,38 +895,38 @@
       <c r="C15" s="15">
         <v>1</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>0</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H15" s="14">
-        <v>-66.666666666666</v>
+        <v>-25</v>
       </c>
       <c r="I15" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J15" s="15">
         <v>7</v>
       </c>
       <c r="K15" s="14">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="L15" s="14">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="M15" s="14">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="N15" s="14">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="14">
         <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G16" s="15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H16" s="14">
         <v>0</v>
       </c>
       <c r="I16" s="15">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J16" s="15">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K16" s="14">
-        <v>14.285714285714</v>
+        <v>12.903225806451</v>
       </c>
       <c r="L16" s="14">
-        <v>-27.272727272727</v>
+        <v>-30</v>
       </c>
       <c r="M16" s="14">
-        <v>-11.111111111111</v>
+        <v>-10.256410256410</v>
       </c>
       <c r="N16" s="14">
-        <v>-73.109243697479</v>
+        <v>-74.452554744525</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D17" s="15">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E17" s="14">
-        <v>-53.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F17" s="15">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G17" s="15">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H17" s="14">
-        <v>-20</v>
+        <v>-26.470588235294</v>
       </c>
       <c r="I17" s="15">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J17" s="15">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K17" s="14">
-        <v>-32.467532467532</v>
+        <v>-31.325301204819</v>
       </c>
       <c r="L17" s="14">
-        <v>-29.729729729729</v>
+        <v>-31.325301204819</v>
       </c>
       <c r="M17" s="14">
-        <v>-21.212121212121</v>
+        <v>-22.972972972973</v>
       </c>
       <c r="N17" s="14">
-        <v>-1.886792452830</v>
+        <v>-9.523809523809</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E18" s="14">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="15">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G18" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H18" s="14">
-        <v>-31.578947368421</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="I18" s="15">
         <v>25</v>
       </c>
       <c r="J18" s="15">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="K18" s="14">
-        <v>-24.242424242424</v>
+        <v>-35.897435897435</v>
       </c>
       <c r="L18" s="14">
-        <v>-7.407407407407</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="M18" s="14">
-        <v>-21.875</v>
+        <v>-32.432432432432</v>
       </c>
       <c r="N18" s="14">
-        <v>-79.838709677419</v>
+        <v>-82.638888888888</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D19" s="15">
         <v>4</v>
       </c>
       <c r="E19" s="14">
-        <v>-50</v>
+        <v>25</v>
       </c>
       <c r="F19" s="15">
         <v>18</v>
       </c>
       <c r="G19" s="15">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H19" s="14">
-        <v>-5.263157894736</v>
+        <v>38.461538461538</v>
       </c>
       <c r="I19" s="15">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="J19" s="15">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K19" s="14">
-        <v>-11.764705882352</v>
+        <v>-7.272727272727</v>
       </c>
       <c r="L19" s="14">
-        <v>-28.571428571428</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="M19" s="14">
-        <v>0</v>
+        <v>8.510638297872</v>
       </c>
       <c r="N19" s="14">
-        <v>-21.052631578947</v>
+        <v>-17.741935483871</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="15">
+        <v>3</v>
       </c>
       <c r="D20" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" s="14">
-        <v>-100</v>
+        <v>50</v>
       </c>
       <c r="F20" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G20" s="15">
         <v>11</v>
       </c>
       <c r="H20" s="14">
-        <v>-72.727272727272</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="I20" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J20" s="15">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K20" s="14">
-        <v>-76.923076923076</v>
+        <v>-67.857142857142</v>
       </c>
       <c r="L20" s="14">
-        <v>-78.571428571428</v>
+        <v>-70</v>
       </c>
       <c r="M20" s="14">
-        <v>-53.846153846153</v>
+        <v>-40</v>
       </c>
       <c r="N20" s="14">
-        <v>-90.322580645161</v>
+        <v>-86.764705882352</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>-55.172413793103</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="F21" s="17">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G21" s="17">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="H21" s="18">
-        <v>-25.242718446601</v>
+        <v>-22.105263157894</v>
       </c>
       <c r="I21" s="17">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="J21" s="17">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="K21" s="18">
-        <v>-25.225225225225</v>
+        <v>-24.279835390946</v>
       </c>
       <c r="L21" s="18">
-        <v>-31.967213114754</v>
+        <v>-31.598513011152</v>
       </c>
       <c r="M21" s="18">
-        <v>-13.989637305699</v>
+        <v>-13.615023474178</v>
       </c>
       <c r="N21" s="18">
-        <v>-60.941176470588</v>
+        <v>-62.061855670103</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,7 +1180,7 @@
         <v>29</v>
       </c>
       <c r="C22" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,19 +1198,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J22" s="15">
         <v>3</v>
       </c>
       <c r="K22" s="14">
-        <v>33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="L22" s="14">
         <v>0</v>
       </c>
       <c r="M22" s="14">
-        <v>33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D24" s="15">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E24" s="14">
-        <v>-50</v>
+        <v>-34.782608695652</v>
       </c>
       <c r="F24" s="15">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G24" s="15">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H24" s="14">
-        <v>-32.432432432432</v>
+        <v>-32.911392405063</v>
       </c>
       <c r="I24" s="15">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="J24" s="15">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="K24" s="14">
-        <v>-32.624113475177</v>
+        <v>-32.317073170731</v>
       </c>
       <c r="L24" s="14">
-        <v>-20.833333333333</v>
+        <v>-19.565217391304</v>
       </c>
       <c r="M24" s="14">
-        <v>28.378378378378</v>
+        <v>29.069767441860</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="15">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E25" s="14">
-        <v>0</v>
+        <v>-90.909090909090</v>
       </c>
       <c r="F25" s="15">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G25" s="15">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H25" s="14">
-        <v>-12.5</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="I25" s="15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J25" s="15">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K25" s="14">
-        <v>-40</v>
+        <v>-50.980392156862</v>
       </c>
       <c r="L25" s="14">
-        <v>-36.842105263157</v>
+        <v>-39.024390243902</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D26" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E26" s="14">
-        <v>12.5</v>
+        <v>128.571428571429</v>
       </c>
       <c r="F26" s="15">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G26" s="15">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H26" s="14">
-        <v>-28.571428571428</v>
+        <v>-10.416666666666</v>
       </c>
       <c r="I26" s="15">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="J26" s="15">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="K26" s="14">
-        <v>3.092783505154</v>
+        <v>11.538461538461</v>
       </c>
       <c r="L26" s="14">
-        <v>-6.542056074766</v>
+        <v>0</v>
       </c>
       <c r="M26" s="14">
-        <v>14.942528735632</v>
+        <v>19.587628865979</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="15">
         <v>1</v>
       </c>
-      <c r="D27" s="15">
-        <v>2</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-50</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H27" s="14">
-        <v>-80</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I27" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J27" s="15">
         <v>13</v>
       </c>
       <c r="K27" s="14">
-        <v>-53.846153846153</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="L27" s="14">
-        <v>-50</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,17 +1428,17 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="15">
-        <v>4</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G28" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H28" s="14">
         <v>-100</v>
@@ -1453,7 +1453,7 @@
         <v>-92.857142857142</v>
       </c>
       <c r="L28" s="14">
-        <v>-93.75</v>
+        <v>-94.444444444444</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="15">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1497,18 +1497,18 @@
         <v>-75</v>
       </c>
       <c r="M29" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="N29" s="14">
-        <v>-90.909090909090</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="15">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1538,10 +1538,10 @@
         <v>-66.666666666666</v>
       </c>
       <c r="M30" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="N30" s="14">
-        <v>-90.909090909090</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-041pct.xlsx
+++ b/data/source/weekly/cs-en-us-041pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -895,26 +895,26 @@
       <c r="C15" s="15">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>0</v>
       </c>
       <c r="F15" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" s="15">
         <v>4</v>
       </c>
       <c r="H15" s="14">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="I15" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J15" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K15" s="14">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="M15" s="14">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="N15" s="14">
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>3</v>
       </c>
       <c r="D16" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F16" s="15">
         <v>12</v>
       </c>
       <c r="G16" s="15">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H16" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I16" s="15">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J16" s="15">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K16" s="14">
-        <v>12.903225806451</v>
+        <v>18.75</v>
       </c>
       <c r="L16" s="14">
-        <v>-30</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="M16" s="14">
-        <v>-10.256410256410</v>
+        <v>-11.627906976744</v>
       </c>
       <c r="N16" s="14">
-        <v>-74.452554744525</v>
+        <v>-75.324675324675</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" s="15">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E17" s="14">
-        <v>-16.666666666666</v>
+        <v>-62.5</v>
       </c>
       <c r="F17" s="15">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G17" s="15">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H17" s="14">
-        <v>-26.470588235294</v>
+        <v>-41.025641025641</v>
       </c>
       <c r="I17" s="15">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="J17" s="15">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="K17" s="14">
-        <v>-31.325301204819</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="L17" s="14">
-        <v>-31.325301204819</v>
+        <v>-30</v>
       </c>
       <c r="M17" s="14">
-        <v>-22.972972972973</v>
+        <v>-25.882352941176</v>
       </c>
       <c r="N17" s="14">
-        <v>-9.523809523809</v>
+        <v>-13.698630136986</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="15">
+        <v>3</v>
       </c>
       <c r="D18" s="15">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E18" s="14">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="F18" s="15">
         <v>11</v>
       </c>
       <c r="G18" s="15">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H18" s="14">
-        <v>-47.619047619047</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="I18" s="15">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J18" s="15">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K18" s="14">
-        <v>-35.897435897435</v>
+        <v>-30</v>
       </c>
       <c r="L18" s="14">
-        <v>-13.793103448275</v>
+        <v>-9.677419354838</v>
       </c>
       <c r="M18" s="14">
-        <v>-32.432432432432</v>
+        <v>-31.707317073170</v>
       </c>
       <c r="N18" s="14">
-        <v>-82.638888888888</v>
+        <v>-82.165605095541</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D19" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E19" s="14">
-        <v>25</v>
+        <v>-50</v>
       </c>
       <c r="F19" s="15">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G19" s="15">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H19" s="14">
-        <v>38.461538461538</v>
+        <v>-18.75</v>
       </c>
       <c r="I19" s="15">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J19" s="15">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="K19" s="14">
-        <v>-7.272727272727</v>
+        <v>-11.475409836065</v>
       </c>
       <c r="L19" s="14">
-        <v>-26.086956521739</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M19" s="14">
-        <v>8.510638297872</v>
+        <v>10.204081632653</v>
       </c>
       <c r="N19" s="14">
-        <v>-17.741935483871</v>
+        <v>-19.402985074626</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" s="15">
         <v>2</v>
       </c>
       <c r="E20" s="14">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="15">
         <v>5</v>
       </c>
       <c r="G20" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H20" s="14">
-        <v>-54.545454545454</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="I20" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J20" s="15">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K20" s="14">
-        <v>-67.857142857142</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L20" s="14">
-        <v>-70</v>
+        <v>-67.741935483871</v>
       </c>
       <c r="M20" s="14">
-        <v>-40</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N20" s="14">
-        <v>-86.764705882352</v>
+        <v>-86.111111111111</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,37 +1142,37 @@
         <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E21" s="18">
-        <v>-19.047619047619</v>
+        <v>-37.037037037037</v>
       </c>
       <c r="F21" s="17">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G21" s="17">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H21" s="18">
-        <v>-22.105263157894</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="I21" s="17">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="J21" s="17">
-        <v>243</v>
+        <v>270</v>
       </c>
       <c r="K21" s="18">
-        <v>-24.279835390946</v>
+        <v>-25.555555555555</v>
       </c>
       <c r="L21" s="18">
-        <v>-31.598513011152</v>
+        <v>-31.632653061224</v>
       </c>
       <c r="M21" s="18">
-        <v>-13.615023474178</v>
+        <v>-14.468085106383</v>
       </c>
       <c r="N21" s="18">
-        <v>-62.061855670103</v>
+        <v>-62.359550561797</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="15">
+        <v>1</v>
+      </c>
+      <c r="D22" s="15">
         <v>2</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="E22" s="14">
+        <v>-50</v>
       </c>
       <c r="F22" s="15">
+        <v>6</v>
+      </c>
+      <c r="G22" s="15">
+        <v>2</v>
+      </c>
+      <c r="H22" s="14">
+        <v>200</v>
+      </c>
+      <c r="I22" s="15">
+        <v>7</v>
+      </c>
+      <c r="J22" s="15">
         <v>5</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I22" s="15">
-        <v>6</v>
-      </c>
-      <c r="J22" s="15">
-        <v>3</v>
-      </c>
       <c r="K22" s="14">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="L22" s="14">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M22" s="14">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1223,29 +1223,29 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" s="15">
+      <c r="D23" s="15">
         <v>1</v>
       </c>
-      <c r="G23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>21</v>
+      <c r="E23" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="15">
+        <v>1</v>
+      </c>
+      <c r="H23" s="14">
+        <v>-100</v>
       </c>
       <c r="I23" s="15">
         <v>1</v>
       </c>
       <c r="J23" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K23" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L23" s="14">
         <v>-83.333333333333</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D24" s="15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E24" s="14">
-        <v>-34.782608695652</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F24" s="15">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G24" s="15">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H24" s="14">
-        <v>-32.911392405063</v>
+        <v>-34.523809523809</v>
       </c>
       <c r="I24" s="15">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="J24" s="15">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="K24" s="14">
-        <v>-32.317073170731</v>
+        <v>-32.446808510638</v>
       </c>
       <c r="L24" s="14">
-        <v>-19.565217391304</v>
+        <v>-15.333333333333</v>
       </c>
       <c r="M24" s="14">
-        <v>29.069767441860</v>
+        <v>38.043478260869</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D25" s="15">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E25" s="14">
-        <v>-90.909090909090</v>
+        <v>0</v>
       </c>
       <c r="F25" s="15">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G25" s="15">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H25" s="14">
-        <v>-58.333333333333</v>
+        <v>-31.818181818181</v>
       </c>
       <c r="I25" s="15">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J25" s="15">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="K25" s="14">
-        <v>-50.980392156862</v>
+        <v>-45.614035087719</v>
       </c>
       <c r="L25" s="14">
-        <v>-39.024390243902</v>
+        <v>-27.906976744186</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D26" s="15">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E26" s="14">
-        <v>128.571428571429</v>
+        <v>0</v>
       </c>
       <c r="F26" s="15">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G26" s="15">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="H26" s="14">
-        <v>-10.416666666666</v>
+        <v>9.756097560975</v>
       </c>
       <c r="I26" s="15">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="J26" s="15">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="K26" s="14">
-        <v>11.538461538461</v>
+        <v>10.256410256410</v>
       </c>
       <c r="L26" s="14">
-        <v>0</v>
+        <v>-8.510638297872</v>
       </c>
       <c r="M26" s="14">
-        <v>19.587628865979</v>
+        <v>20.560747663551</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="15">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>0</v>
       </c>
       <c r="F27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H27" s="14">
-        <v>-57.142857142857</v>
+        <v>-20</v>
       </c>
       <c r="I27" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J27" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K27" s="14">
-        <v>-46.153846153846</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L27" s="14">
-        <v>-41.666666666666</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,17 +1428,17 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="15">
+        <v>4</v>
+      </c>
+      <c r="E28" s="14">
+        <v>-100</v>
       </c>
       <c r="F28" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G28" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H28" s="14">
         <v>-100</v>
@@ -1447,13 +1447,13 @@
         <v>1</v>
       </c>
       <c r="J28" s="15">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K28" s="14">
-        <v>-92.857142857142</v>
+        <v>-94.444444444444</v>
       </c>
       <c r="L28" s="14">
-        <v>-94.444444444444</v>
+        <v>-95</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1494,13 +1494,13 @@
         <v>21</v>
       </c>
       <c r="L29" s="14">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="M29" s="14">
         <v>-75</v>
       </c>
       <c r="N29" s="14">
-        <v>-92.307692307692</v>
+        <v>-93.333333333333</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1535,13 +1535,13 @@
         <v>21</v>
       </c>
       <c r="L30" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="M30" s="14">
         <v>-75</v>
       </c>
       <c r="N30" s="14">
-        <v>-92.307692307692</v>
+        <v>-93.333333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-041pct.xlsx
+++ b/data/source/weekly/cs-en-us-041pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -892,23 +892,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
-        <v>1</v>
-      </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>0</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I15" s="15">
         <v>8</v>
@@ -926,7 +926,7 @@
         <v>300</v>
       </c>
       <c r="N15" s="14">
-        <v>100</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" s="15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E16" s="14">
-        <v>200</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="15">
         <v>12</v>
       </c>
       <c r="G16" s="15">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H16" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I16" s="15">
+        <v>42</v>
+      </c>
+      <c r="J16" s="15">
         <v>38</v>
       </c>
-      <c r="J16" s="15">
-        <v>32</v>
-      </c>
       <c r="K16" s="14">
-        <v>18.75</v>
+        <v>10.526315789473</v>
       </c>
       <c r="L16" s="14">
-        <v>-26.923076923076</v>
+        <v>-27.586206896551</v>
       </c>
       <c r="M16" s="14">
-        <v>-11.627906976744</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="N16" s="14">
-        <v>-75.324675324675</v>
+        <v>-75.438596491228</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" s="15">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E17" s="14">
-        <v>-62.5</v>
+        <v>133.333333333333</v>
       </c>
       <c r="F17" s="15">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G17" s="15">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H17" s="14">
-        <v>-41.025641025641</v>
+        <v>-37.5</v>
       </c>
       <c r="I17" s="15">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="J17" s="15">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K17" s="14">
-        <v>-36.363636363636</v>
+        <v>-30.392156862745</v>
       </c>
       <c r="L17" s="14">
-        <v>-30</v>
+        <v>-30.392156862745</v>
       </c>
       <c r="M17" s="14">
-        <v>-25.882352941176</v>
+        <v>-21.111111111111</v>
       </c>
       <c r="N17" s="14">
-        <v>-13.698630136986</v>
+        <v>-13.414634146341</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F18" s="15">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G18" s="15">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H18" s="14">
-        <v>-35.294117647058</v>
+        <v>-50</v>
       </c>
       <c r="I18" s="15">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J18" s="15">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K18" s="14">
-        <v>-30</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L18" s="14">
-        <v>-9.677419354838</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="M18" s="14">
-        <v>-31.707317073170</v>
+        <v>-42.307692307692</v>
       </c>
       <c r="N18" s="14">
-        <v>-82.165605095541</v>
+        <v>-82.035928143712</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D19" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" s="14">
-        <v>-50</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F19" s="15">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G19" s="15">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H19" s="14">
-        <v>-18.75</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="I19" s="15">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="J19" s="15">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="K19" s="14">
-        <v>-11.475409836065</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="L19" s="14">
-        <v>-33.333333333333</v>
+        <v>-35.483870967741</v>
       </c>
       <c r="M19" s="14">
-        <v>10.204081632653</v>
+        <v>3.448275862068</v>
       </c>
       <c r="N19" s="14">
-        <v>-19.402985074626</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D20" s="15">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E20" s="14">
-        <v>-50</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="F20" s="15">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G20" s="15">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H20" s="14">
-        <v>-58.333333333333</v>
+        <v>-55</v>
       </c>
       <c r="I20" s="15">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J20" s="15">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K20" s="14">
-        <v>-66.666666666666</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="L20" s="14">
-        <v>-67.741935483871</v>
+        <v>-55.882352941176</v>
       </c>
       <c r="M20" s="14">
-        <v>-33.333333333333</v>
+        <v>-6.25</v>
       </c>
       <c r="N20" s="14">
-        <v>-86.111111111111</v>
+        <v>-80.519480519480</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D21" s="17">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E21" s="18">
-        <v>-37.037037037037</v>
+        <v>-20</v>
       </c>
       <c r="F21" s="17">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G21" s="17">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="H21" s="18">
-        <v>-29.166666666666</v>
+        <v>-33.644859813084</v>
       </c>
       <c r="I21" s="17">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="J21" s="17">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="K21" s="18">
-        <v>-25.555555555555</v>
+        <v>-24.666666666666</v>
       </c>
       <c r="L21" s="18">
-        <v>-31.632653061224</v>
+        <v>-31.515151515151</v>
       </c>
       <c r="M21" s="18">
-        <v>-14.468085106383</v>
+        <v>-15.355805243445</v>
       </c>
       <c r="N21" s="18">
-        <v>-62.359550561797</v>
+        <v>-61.301369863013</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,28 +1189,28 @@
         <v>-50</v>
       </c>
       <c r="F22" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G22" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H22" s="14">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="I22" s="15">
+        <v>8</v>
+      </c>
+      <c r="J22" s="15">
         <v>7</v>
       </c>
-      <c r="J22" s="15">
-        <v>5</v>
-      </c>
       <c r="K22" s="14">
-        <v>40</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L22" s="14">
-        <v>16.666666666666</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M22" s="14">
-        <v>133.333333333333</v>
+        <v>100</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="15">
+      <c r="C23" s="15">
         <v>1</v>
       </c>
-      <c r="E23" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>20</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="15">
+        <v>1</v>
       </c>
       <c r="G23" s="15">
         <v>1</v>
       </c>
       <c r="H23" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I23" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23" s="15">
         <v>2</v>
       </c>
       <c r="K23" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L23" s="14">
-        <v>-83.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M23" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D24" s="15">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E24" s="14">
-        <v>-33.333333333333</v>
+        <v>111.111111111111</v>
       </c>
       <c r="F24" s="15">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G24" s="15">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="H24" s="14">
-        <v>-34.523809523809</v>
+        <v>-18.055555555555</v>
       </c>
       <c r="I24" s="15">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="J24" s="15">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="K24" s="14">
-        <v>-32.446808510638</v>
+        <v>-25.888324873096</v>
       </c>
       <c r="L24" s="14">
-        <v>-15.333333333333</v>
+        <v>-9.876543209876</v>
       </c>
       <c r="M24" s="14">
-        <v>38.043478260869</v>
+        <v>47.474747474747</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D25" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E25" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="F25" s="15">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G25" s="15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H25" s="14">
-        <v>-31.818181818181</v>
+        <v>-47.826086956521</v>
       </c>
       <c r="I25" s="15">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J25" s="15">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K25" s="14">
-        <v>-45.614035087719</v>
+        <v>-44.262295081967</v>
       </c>
       <c r="L25" s="14">
-        <v>-27.906976744186</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D26" s="15">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E26" s="14">
         <v>0</v>
       </c>
       <c r="F26" s="15">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G26" s="15">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="H26" s="14">
-        <v>9.756097560975</v>
+        <v>30.555555555555</v>
       </c>
       <c r="I26" s="15">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="J26" s="15">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="K26" s="14">
-        <v>10.256410256410</v>
+        <v>9.6</v>
       </c>
       <c r="L26" s="14">
-        <v>-8.510638297872</v>
+        <v>-9.271523178807</v>
       </c>
       <c r="M26" s="14">
-        <v>20.560747663551</v>
+        <v>19.130434782608</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="15">
         <v>1</v>
       </c>
       <c r="E27" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="15">
+        <v>3</v>
+      </c>
+      <c r="G27" s="15">
         <v>4</v>
       </c>
-      <c r="G27" s="15">
-        <v>5</v>
-      </c>
       <c r="H27" s="14">
-        <v>-20</v>
+        <v>-25</v>
       </c>
       <c r="I27" s="15">
         <v>8</v>
       </c>
       <c r="J27" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K27" s="14">
-        <v>-42.857142857142</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="L27" s="14">
         <v>-52.941176470588</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="15">
+        <v>2</v>
       </c>
       <c r="D28" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E28" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="F28" s="15">
+        <v>2</v>
       </c>
       <c r="G28" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H28" s="14">
-        <v>-100</v>
+        <v>-80</v>
       </c>
       <c r="I28" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J28" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K28" s="14">
-        <v>-94.444444444444</v>
+        <v>-85</v>
       </c>
       <c r="L28" s="14">
-        <v>-95</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1494,13 +1494,13 @@
         <v>21</v>
       </c>
       <c r="L29" s="14">
-        <v>-80</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="M29" s="14">
         <v>-75</v>
       </c>
       <c r="N29" s="14">
-        <v>-93.333333333333</v>
+        <v>-94.444444444444</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1535,13 +1535,13 @@
         <v>21</v>
       </c>
       <c r="L30" s="14">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="M30" s="14">
         <v>-75</v>
       </c>
       <c r="N30" s="14">
-        <v>-93.333333333333</v>
+        <v>-94.444444444444</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-041pct.xlsx
+++ b/data/source/weekly/cs-en-us-041pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -895,38 +895,38 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="15">
         <v>2</v>
       </c>
       <c r="H15" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I15" s="15">
         <v>8</v>
       </c>
       <c r="J15" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K15" s="14">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L15" s="14">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M15" s="14">
-        <v>300</v>
+        <v>166.666666666667</v>
       </c>
       <c r="N15" s="14">
-        <v>60</v>
+        <v>33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,10 +934,10 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E16" s="14">
         <v>-33.333333333333</v>
@@ -946,28 +946,28 @@
         <v>12</v>
       </c>
       <c r="G16" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H16" s="14">
-        <v>0</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="I16" s="15">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J16" s="15">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K16" s="14">
-        <v>10.526315789473</v>
+        <v>7.317073170731</v>
       </c>
       <c r="L16" s="14">
-        <v>-27.586206896551</v>
+        <v>-30.158730158730</v>
       </c>
       <c r="M16" s="14">
-        <v>-14.285714285714</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="N16" s="14">
-        <v>-75.438596491228</v>
+        <v>-76.216216216216</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D17" s="15">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E17" s="14">
-        <v>133.333333333333</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F17" s="15">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G17" s="15">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H17" s="14">
-        <v>-37.5</v>
+        <v>-32.352941176470</v>
       </c>
       <c r="I17" s="15">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J17" s="15">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="K17" s="14">
-        <v>-30.392156862745</v>
+        <v>-31.531531531531</v>
       </c>
       <c r="L17" s="14">
-        <v>-30.392156862745</v>
+        <v>-31.531531531531</v>
       </c>
       <c r="M17" s="14">
-        <v>-21.111111111111</v>
+        <v>-22.448979591836</v>
       </c>
       <c r="N17" s="14">
-        <v>-13.414634146341</v>
+        <v>-8.433734939759</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>2</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E18" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G18" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H18" s="14">
-        <v>-50</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="I18" s="15">
         <v>30</v>
       </c>
       <c r="J18" s="15">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K18" s="14">
-        <v>-28.571428571428</v>
+        <v>-34.782608695652</v>
       </c>
       <c r="L18" s="14">
-        <v>-11.764705882352</v>
+        <v>-18.918918918918</v>
       </c>
       <c r="M18" s="14">
-        <v>-42.307692307692</v>
+        <v>-49.152542372881</v>
       </c>
       <c r="N18" s="14">
-        <v>-82.035928143712</v>
+        <v>-83.695652173913</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>6</v>
       </c>
       <c r="D19" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E19" s="14">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="F19" s="15">
+        <v>20</v>
+      </c>
+      <c r="G19" s="15">
+        <v>26</v>
+      </c>
+      <c r="H19" s="14">
+        <v>-23.076923076923</v>
+      </c>
+      <c r="I19" s="15">
+        <v>66</v>
+      </c>
+      <c r="J19" s="15">
+        <v>77</v>
+      </c>
+      <c r="K19" s="14">
         <v>-14.285714285714</v>
       </c>
-      <c r="F19" s="15">
-        <v>16</v>
-      </c>
-      <c r="G19" s="15">
-        <v>21</v>
-      </c>
-      <c r="H19" s="14">
-        <v>-23.809523809523</v>
-      </c>
-      <c r="I19" s="15">
-        <v>60</v>
-      </c>
-      <c r="J19" s="15">
-        <v>68</v>
-      </c>
-      <c r="K19" s="14">
-        <v>-11.764705882352</v>
-      </c>
       <c r="L19" s="14">
-        <v>-35.483870967741</v>
+        <v>-32.653061224489</v>
       </c>
       <c r="M19" s="14">
-        <v>3.448275862068</v>
+        <v>6.451612903225</v>
       </c>
       <c r="N19" s="14">
-        <v>-20</v>
+        <v>-18.518518518518</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D20" s="15">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E20" s="14">
-        <v>-58.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G20" s="15">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H20" s="14">
-        <v>-55</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I20" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J20" s="15">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K20" s="14">
-        <v>-64.285714285714</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="L20" s="14">
-        <v>-55.882352941176</v>
+        <v>-56.756756756756</v>
       </c>
       <c r="M20" s="14">
-        <v>-6.25</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="N20" s="14">
-        <v>-80.519480519480</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,63 +1139,63 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E21" s="18">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="F21" s="17">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G21" s="17">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H21" s="18">
-        <v>-33.644859813084</v>
+        <v>-32.075471698113</v>
       </c>
       <c r="I21" s="17">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="J21" s="17">
-        <v>300</v>
+        <v>328</v>
       </c>
       <c r="K21" s="18">
-        <v>-24.666666666666</v>
+        <v>-26.829268292682</v>
       </c>
       <c r="L21" s="18">
-        <v>-31.515151515151</v>
+        <v>-32.584269662921</v>
       </c>
       <c r="M21" s="18">
-        <v>-15.355805243445</v>
+        <v>-19.191919191919</v>
       </c>
       <c r="N21" s="18">
-        <v>-61.301369863013</v>
+        <v>-61.722488038277</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>1</v>
-      </c>
-      <c r="D22" s="15">
-        <v>2</v>
-      </c>
-      <c r="E22" s="14">
-        <v>-50</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G22" s="15">
         <v>4</v>
       </c>
       <c r="H22" s="14">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I22" s="15">
         <v>8</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
+        <v>16</v>
+      </c>
+      <c r="D24" s="15">
         <v>19</v>
       </c>
-      <c r="D24" s="15">
-        <v>9</v>
-      </c>
       <c r="E24" s="14">
-        <v>111.111111111111</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="F24" s="15">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G24" s="15">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H24" s="14">
-        <v>-18.055555555555</v>
+        <v>-12</v>
       </c>
       <c r="I24" s="15">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="J24" s="15">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="K24" s="14">
-        <v>-25.888324873096</v>
+        <v>-25</v>
       </c>
       <c r="L24" s="14">
-        <v>-9.876543209876</v>
+        <v>-8.474576271186</v>
       </c>
       <c r="M24" s="14">
-        <v>47.474747474747</v>
+        <v>50</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
+        <v>4</v>
+      </c>
+      <c r="D25" s="15">
         <v>3</v>
       </c>
-      <c r="D25" s="15">
-        <v>4</v>
-      </c>
       <c r="E25" s="14">
-        <v>-25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F25" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G25" s="15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H25" s="14">
-        <v>-47.826086956521</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="I25" s="15">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J25" s="15">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K25" s="14">
-        <v>-44.262295081967</v>
+        <v>-40.625</v>
       </c>
       <c r="L25" s="14">
-        <v>-26.086956521739</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D26" s="15">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E26" s="14">
-        <v>0</v>
+        <v>-47.368421052631</v>
       </c>
       <c r="F26" s="15">
+        <v>48</v>
+      </c>
+      <c r="G26" s="15">
         <v>47</v>
       </c>
-      <c r="G26" s="15">
-        <v>36</v>
-      </c>
       <c r="H26" s="14">
-        <v>30.555555555555</v>
+        <v>2.127659574468</v>
       </c>
       <c r="I26" s="15">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="J26" s="15">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="K26" s="14">
-        <v>9.6</v>
+        <v>2.083333333333</v>
       </c>
       <c r="L26" s="14">
-        <v>-9.271523178807</v>
+        <v>-8.125</v>
       </c>
       <c r="M26" s="14">
-        <v>19.130434782608</v>
+        <v>19.512195121951</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>-100</v>
       </c>
       <c r="F27" s="15">
+        <v>2</v>
+      </c>
+      <c r="G27" s="15">
         <v>3</v>
       </c>
-      <c r="G27" s="15">
-        <v>4</v>
-      </c>
       <c r="H27" s="14">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I27" s="15">
         <v>8</v>
       </c>
       <c r="J27" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K27" s="14">
-        <v>-46.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="L27" s="14">
-        <v>-52.941176470588</v>
+        <v>-60</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E28" s="14">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="F28" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="15">
         <v>10</v>
       </c>
       <c r="H28" s="14">
-        <v>-80</v>
+        <v>-70</v>
       </c>
       <c r="I28" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J28" s="15">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K28" s="14">
-        <v>-85</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="L28" s="14">
-        <v>-85.714285714285</v>
+        <v>-82.608695652173</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="15">
-        <v>1</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1500,7 +1500,7 @@
         <v>-75</v>
       </c>
       <c r="N29" s="14">
-        <v>-94.444444444444</v>
+        <v>-94.736842105263</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="15">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1541,7 +1541,7 @@
         <v>-75</v>
       </c>
       <c r="N30" s="14">
-        <v>-94.444444444444</v>
+        <v>-94.736842105263</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-041pct.xlsx
+++ b/data/source/weekly/cs-en-us-041pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -902,28 +902,28 @@
         <v>-100</v>
       </c>
       <c r="F15" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="14">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I15" s="15">
         <v>8</v>
       </c>
       <c r="J15" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K15" s="14">
-        <v>-11.111111111111</v>
+        <v>-20</v>
       </c>
       <c r="L15" s="14">
         <v>-11.111111111111</v>
       </c>
       <c r="M15" s="14">
-        <v>166.666666666667</v>
+        <v>60</v>
       </c>
       <c r="N15" s="14">
         <v>33.333333333333</v>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>2</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E16" s="14">
-        <v>-33.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="15">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G16" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H16" s="14">
-        <v>-7.692307692307</v>
+        <v>-40</v>
       </c>
       <c r="I16" s="15">
         <v>44</v>
       </c>
       <c r="J16" s="15">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="K16" s="14">
-        <v>7.317073170731</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="L16" s="14">
+        <v>-36.231884057971</v>
+      </c>
+      <c r="M16" s="14">
         <v>-30.158730158730</v>
       </c>
-      <c r="M16" s="14">
-        <v>-24.137931034482</v>
-      </c>
       <c r="N16" s="14">
-        <v>-76.216216216216</v>
+        <v>-78.325123152709</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
+        <v>6</v>
+      </c>
+      <c r="D17" s="15">
         <v>5</v>
       </c>
-      <c r="D17" s="15">
-        <v>9</v>
-      </c>
       <c r="E17" s="14">
-        <v>-44.444444444444</v>
+        <v>20</v>
       </c>
       <c r="F17" s="15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G17" s="15">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H17" s="14">
-        <v>-32.352941176470</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I17" s="15">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="J17" s="15">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="K17" s="14">
-        <v>-31.531531531531</v>
+        <v>-29.310344827586</v>
       </c>
       <c r="L17" s="14">
-        <v>-31.531531531531</v>
+        <v>-29.310344827586</v>
       </c>
       <c r="M17" s="14">
-        <v>-22.448979591836</v>
+        <v>-22.641509433962</v>
       </c>
       <c r="N17" s="14">
-        <v>-8.433734939759</v>
+        <v>-8.888888888888</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="15">
+        <v>2</v>
       </c>
       <c r="D18" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G18" s="15">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H18" s="14">
-        <v>-61.538461538461</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I18" s="15">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J18" s="15">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K18" s="14">
-        <v>-34.782608695652</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L18" s="14">
-        <v>-18.918918918918</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="M18" s="14">
-        <v>-49.152542372881</v>
+        <v>-51.515151515151</v>
       </c>
       <c r="N18" s="14">
-        <v>-83.695652173913</v>
+        <v>-84.313725490196</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D19" s="15">
         <v>9</v>
       </c>
       <c r="E19" s="14">
-        <v>-33.333333333333</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F19" s="15">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G19" s="15">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H19" s="14">
-        <v>-23.076923076923</v>
+        <v>-25.806451612903</v>
       </c>
       <c r="I19" s="15">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="J19" s="15">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K19" s="14">
-        <v>-14.285714285714</v>
+        <v>-13.953488372093</v>
       </c>
       <c r="L19" s="14">
-        <v>-32.653061224489</v>
+        <v>-30.188679245283</v>
       </c>
       <c r="M19" s="14">
-        <v>6.451612903225</v>
+        <v>10.447761194029</v>
       </c>
       <c r="N19" s="14">
-        <v>-18.518518518518</v>
+        <v>-15.909090909090</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1107,31 +1107,31 @@
         <v>-50</v>
       </c>
       <c r="F20" s="15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G20" s="15">
         <v>18</v>
       </c>
       <c r="H20" s="14">
-        <v>-44.444444444444</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="I20" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J20" s="15">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K20" s="14">
-        <v>-63.636363636363</v>
+        <v>-63.043478260869</v>
       </c>
       <c r="L20" s="14">
-        <v>-56.756756756756</v>
+        <v>-58.536585365853</v>
       </c>
       <c r="M20" s="14">
-        <v>-5.882352941176</v>
+        <v>0</v>
       </c>
       <c r="N20" s="14">
-        <v>-80</v>
+        <v>-80.232558139534</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>-50</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="F21" s="17">
         <v>72</v>
       </c>
       <c r="G21" s="17">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H21" s="18">
-        <v>-32.075471698113</v>
+        <v>-33.944954128440</v>
       </c>
       <c r="I21" s="17">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="J21" s="17">
-        <v>328</v>
+        <v>352</v>
       </c>
       <c r="K21" s="18">
-        <v>-26.829268292682</v>
+        <v>-26.988636363636</v>
       </c>
       <c r="L21" s="18">
-        <v>-32.584269662921</v>
+        <v>-33.762886597938</v>
       </c>
       <c r="M21" s="18">
-        <v>-19.191919191919</v>
+        <v>-20.679012345679</v>
       </c>
       <c r="N21" s="18">
-        <v>-61.722488038277</v>
+        <v>-62.481751824817</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,13 +1189,13 @@
         <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G22" s="15">
         <v>4</v>
       </c>
       <c r="H22" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="15">
         <v>8</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="15">
+        <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1230,28 +1230,28 @@
         <v>21</v>
       </c>
       <c r="F23" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="15">
         <v>1</v>
       </c>
       <c r="H23" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I23" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J23" s="15">
         <v>2</v>
       </c>
       <c r="K23" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L23" s="14">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="M23" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D24" s="15">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E24" s="14">
-        <v>-15.789473684210</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="F24" s="15">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G24" s="15">
         <v>75</v>
       </c>
       <c r="H24" s="14">
-        <v>-12</v>
+        <v>-14.666666666666</v>
       </c>
       <c r="I24" s="15">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="J24" s="15">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="K24" s="14">
-        <v>-25</v>
+        <v>-26.778242677824</v>
       </c>
       <c r="L24" s="14">
-        <v>-8.474576271186</v>
+        <v>-10.256410256410</v>
       </c>
       <c r="M24" s="14">
-        <v>50</v>
+        <v>50.862068965517</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D25" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E25" s="14">
-        <v>33.333333333333</v>
+        <v>-60</v>
       </c>
       <c r="F25" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G25" s="15">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H25" s="14">
-        <v>-41.666666666666</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I25" s="15">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J25" s="15">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="K25" s="14">
-        <v>-40.625</v>
+        <v>-42.028985507246</v>
       </c>
       <c r="L25" s="14">
-        <v>-20.833333333333</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D26" s="15">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E26" s="14">
-        <v>-47.368421052631</v>
+        <v>6.25</v>
       </c>
       <c r="F26" s="15">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G26" s="15">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H26" s="14">
-        <v>2.127659574468</v>
+        <v>-12.5</v>
       </c>
       <c r="I26" s="15">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="J26" s="15">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="K26" s="14">
-        <v>2.083333333333</v>
+        <v>2.5</v>
       </c>
       <c r="L26" s="14">
-        <v>-8.125</v>
+        <v>-2.380952380952</v>
       </c>
       <c r="M26" s="14">
-        <v>19.512195121951</v>
+        <v>22.388059701492</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,28 +1388,28 @@
         <v>20</v>
       </c>
       <c r="D27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="14">
         <v>-100</v>
       </c>
       <c r="F27" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H27" s="14">
-        <v>-33.333333333333</v>
+        <v>-80</v>
       </c>
       <c r="I27" s="15">
         <v>8</v>
       </c>
       <c r="J27" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K27" s="14">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L27" s="14">
         <v>-60</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E28" s="14">
-        <v>-75</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
         <v>3</v>
       </c>
       <c r="G28" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H28" s="14">
-        <v>-70</v>
+        <v>-75</v>
       </c>
       <c r="I28" s="15">
         <v>4</v>
       </c>
       <c r="J28" s="15">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K28" s="14">
-        <v>-83.333333333333</v>
+        <v>-84.615384615384</v>
       </c>
       <c r="L28" s="14">
-        <v>-82.608695652173</v>
+        <v>-85.185185185185</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1497,10 +1497,10 @@
         <v>-83.333333333333</v>
       </c>
       <c r="M29" s="14">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="N29" s="14">
-        <v>-94.736842105263</v>
+        <v>-95</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1538,10 +1538,10 @@
         <v>-80</v>
       </c>
       <c r="M30" s="14">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="N30" s="14">
-        <v>-94.736842105263</v>
+        <v>-95</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-041pct.xlsx
+++ b/data/source/weekly/cs-en-us-041pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -895,20 +895,20 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="15">
+        <v>2</v>
+      </c>
+      <c r="H15" s="14">
         <v>-100</v>
-      </c>
-      <c r="F15" s="15">
-        <v>1</v>
-      </c>
-      <c r="G15" s="15">
-        <v>3</v>
-      </c>
-      <c r="H15" s="14">
-        <v>-66.666666666666</v>
       </c>
       <c r="I15" s="15">
         <v>8</v>
@@ -923,51 +923,51 @@
         <v>-11.111111111111</v>
       </c>
       <c r="M15" s="14">
-        <v>60</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N15" s="14">
-        <v>33.333333333333</v>
+        <v>14.285714285714</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="15">
+        <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G16" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H16" s="14">
-        <v>-40</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="I16" s="15">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J16" s="15">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K16" s="14">
-        <v>-4.347826086956</v>
+        <v>-8.163265306122</v>
       </c>
       <c r="L16" s="14">
-        <v>-36.231884057971</v>
+        <v>-39.189189189189</v>
       </c>
       <c r="M16" s="14">
-        <v>-30.158730158730</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="N16" s="14">
-        <v>-78.325123152709</v>
+        <v>-79.638009049773</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D17" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E17" s="14">
-        <v>20</v>
+        <v>-62.5</v>
       </c>
       <c r="F17" s="15">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G17" s="15">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="H17" s="14">
-        <v>-27.272727272727</v>
+        <v>-12</v>
       </c>
       <c r="I17" s="15">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="J17" s="15">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="K17" s="14">
-        <v>-29.310344827586</v>
+        <v>-30.645161290322</v>
       </c>
       <c r="L17" s="14">
-        <v>-29.310344827586</v>
+        <v>-31.746031746031</v>
       </c>
       <c r="M17" s="14">
-        <v>-22.641509433962</v>
+        <v>-23.214285714285</v>
       </c>
       <c r="N17" s="14">
-        <v>-8.888888888888</v>
+        <v>-17.307692307692</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E18" s="14">
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="F18" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G18" s="15">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H18" s="14">
-        <v>-22.222222222222</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="I18" s="15">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J18" s="15">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K18" s="14">
-        <v>-33.333333333333</v>
+        <v>-37.735849056603</v>
       </c>
       <c r="L18" s="14">
-        <v>-30.434782608695</v>
+        <v>-37.735849056603</v>
       </c>
       <c r="M18" s="14">
-        <v>-51.515151515151</v>
+        <v>-52.173913043478</v>
       </c>
       <c r="N18" s="14">
-        <v>-84.313725490196</v>
+        <v>-85.267857142857</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D19" s="15">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E19" s="14">
-        <v>-11.111111111111</v>
+        <v>75</v>
       </c>
       <c r="F19" s="15">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G19" s="15">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H19" s="14">
-        <v>-25.806451612903</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="I19" s="15">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J19" s="15">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="K19" s="14">
-        <v>-13.953488372093</v>
+        <v>-10</v>
       </c>
       <c r="L19" s="14">
-        <v>-30.188679245283</v>
+        <v>-27.027027027027</v>
       </c>
       <c r="M19" s="14">
-        <v>10.447761194029</v>
+        <v>15.714285714285</v>
       </c>
       <c r="N19" s="14">
-        <v>-15.909090909090</v>
+        <v>-13.829787234042</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E20" s="14">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="F20" s="15">
         <v>8</v>
       </c>
       <c r="G20" s="15">
+        <v>21</v>
+      </c>
+      <c r="H20" s="14">
+        <v>-61.904761904761</v>
+      </c>
+      <c r="I20" s="15">
         <v>18</v>
       </c>
-      <c r="H20" s="14">
-        <v>-55.555555555555</v>
-      </c>
-      <c r="I20" s="15">
-        <v>17</v>
-      </c>
       <c r="J20" s="15">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="K20" s="14">
-        <v>-63.043478260869</v>
+        <v>-64.705882352941</v>
       </c>
       <c r="L20" s="14">
-        <v>-58.536585365853</v>
+        <v>-59.090909090909</v>
       </c>
       <c r="M20" s="14">
         <v>0</v>
       </c>
       <c r="N20" s="14">
-        <v>-80.232558139534</v>
+        <v>-80.851063829787</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E21" s="18">
-        <v>-29.166666666666</v>
+        <v>-44</v>
       </c>
       <c r="F21" s="17">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G21" s="17">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H21" s="18">
-        <v>-33.944954128440</v>
+        <v>-35.514018691588</v>
       </c>
       <c r="I21" s="17">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="J21" s="17">
-        <v>352</v>
+        <v>377</v>
       </c>
       <c r="K21" s="18">
-        <v>-26.988636363636</v>
+        <v>-28.116710875331</v>
       </c>
       <c r="L21" s="18">
-        <v>-33.762886597938</v>
+        <v>-35.167464114832</v>
       </c>
       <c r="M21" s="18">
-        <v>-20.679012345679</v>
+        <v>-20.294117647058</v>
       </c>
       <c r="N21" s="18">
-        <v>-62.481751824817</v>
+        <v>-63.962765957446</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,10 +1189,10 @@
         <v>21</v>
       </c>
       <c r="F22" s="15">
+        <v>1</v>
+      </c>
+      <c r="G22" s="15">
         <v>2</v>
-      </c>
-      <c r="G22" s="15">
-        <v>4</v>
       </c>
       <c r="H22" s="14">
         <v>-50</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1232,11 +1232,11 @@
       <c r="F23" s="15">
         <v>2</v>
       </c>
-      <c r="G23" s="15">
-        <v>1</v>
-      </c>
-      <c r="H23" s="14">
-        <v>100</v>
+      <c r="G23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I23" s="15">
         <v>3</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D24" s="15">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E24" s="14">
-        <v>-43.478260869565</v>
+        <v>41.666666666666</v>
       </c>
       <c r="F24" s="15">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G24" s="15">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="H24" s="14">
-        <v>-14.666666666666</v>
+        <v>3.174603174603</v>
       </c>
       <c r="I24" s="15">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="J24" s="15">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="K24" s="14">
-        <v>-26.778242677824</v>
+        <v>-23.505976095617</v>
       </c>
       <c r="L24" s="14">
-        <v>-10.256410256410</v>
+        <v>-8.571428571428</v>
       </c>
       <c r="M24" s="14">
-        <v>50.862068965517</v>
+        <v>45.454545454545</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D25" s="15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E25" s="14">
-        <v>-60</v>
+        <v>500</v>
       </c>
       <c r="F25" s="15">
         <v>15</v>
       </c>
       <c r="G25" s="15">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H25" s="14">
-        <v>-16.666666666666</v>
+        <v>15.384615384615</v>
       </c>
       <c r="I25" s="15">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J25" s="15">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K25" s="14">
-        <v>-42.028985507246</v>
+        <v>-34.285714285714</v>
       </c>
       <c r="L25" s="14">
-        <v>-23.076923076923</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D26" s="15">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E26" s="14">
-        <v>6.25</v>
+        <v>50</v>
       </c>
       <c r="F26" s="15">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G26" s="15">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H26" s="14">
-        <v>-12.5</v>
+        <v>-5.660377358490</v>
       </c>
       <c r="I26" s="15">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="J26" s="15">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="K26" s="14">
-        <v>2.5</v>
+        <v>5.294117647058</v>
       </c>
       <c r="L26" s="14">
-        <v>-2.380952380952</v>
+        <v>2.285714285714</v>
       </c>
       <c r="M26" s="14">
-        <v>22.388059701492</v>
+        <v>26.056338028169</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1393,23 +1393,23 @@
       <c r="E27" s="14">
         <v>-100</v>
       </c>
-      <c r="F27" s="15">
-        <v>1</v>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H27" s="14">
-        <v>-80</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="15">
         <v>8</v>
       </c>
       <c r="J27" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K27" s="14">
-        <v>-55.555555555555</v>
+        <v>-60</v>
       </c>
       <c r="L27" s="14">
         <v>-60</v>
@@ -1438,22 +1438,22 @@
         <v>3</v>
       </c>
       <c r="G28" s="15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H28" s="14">
-        <v>-75</v>
+        <v>-70</v>
       </c>
       <c r="I28" s="15">
         <v>4</v>
       </c>
       <c r="J28" s="15">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K28" s="14">
-        <v>-84.615384615384</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="L28" s="14">
-        <v>-85.185185185185</v>
+        <v>-86.206896551724</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>-80</v>
       </c>
       <c r="N29" s="14">
-        <v>-95</v>
+        <v>-95.454545454545</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>-80</v>
       </c>
       <c r="N30" s="14">
-        <v>-95</v>
+        <v>-95.238095238095</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-041pct.xlsx
+++ b/data/source/weekly/cs-en-us-041pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -895,17 +895,17 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="14">
         <v>-100</v>
@@ -914,10 +914,10 @@
         <v>8</v>
       </c>
       <c r="J15" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K15" s="14">
-        <v>-20</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="L15" s="14">
         <v>-11.111111111111</v>
@@ -926,7 +926,7 @@
         <v>33.333333333333</v>
       </c>
       <c r="N15" s="14">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E16" s="14">
-        <v>-66.666666666666</v>
+        <v>-40</v>
       </c>
       <c r="F16" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G16" s="15">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H16" s="14">
-        <v>-58.823529411764</v>
+        <v>-62.5</v>
       </c>
       <c r="I16" s="15">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J16" s="15">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="K16" s="14">
-        <v>-8.163265306122</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L16" s="14">
-        <v>-39.189189189189</v>
+        <v>-39.240506329113</v>
       </c>
       <c r="M16" s="14">
-        <v>-30.769230769230</v>
+        <v>-31.428571428571</v>
       </c>
       <c r="N16" s="14">
-        <v>-79.638009049773</v>
+        <v>-79.661016949152</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D17" s="15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E17" s="14">
-        <v>-62.5</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="F17" s="15">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G17" s="15">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H17" s="14">
-        <v>-12</v>
+        <v>-42.424242424242</v>
       </c>
       <c r="I17" s="15">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="J17" s="15">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="K17" s="14">
-        <v>-30.645161290322</v>
+        <v>-32.592592592592</v>
       </c>
       <c r="L17" s="14">
-        <v>-31.746031746031</v>
+        <v>-30.534351145038</v>
       </c>
       <c r="M17" s="14">
-        <v>-23.214285714285</v>
+        <v>-25.409836065573</v>
       </c>
       <c r="N17" s="14">
-        <v>-17.307692307692</v>
+        <v>-22.222222222222</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E18" s="14">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="F18" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G18" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H18" s="14">
-        <v>-61.538461538461</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="I18" s="15">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J18" s="15">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K18" s="14">
-        <v>-37.735849056603</v>
+        <v>-35.087719298245</v>
       </c>
       <c r="L18" s="14">
-        <v>-37.735849056603</v>
+        <v>-33.928571428571</v>
       </c>
       <c r="M18" s="14">
-        <v>-52.173913043478</v>
+        <v>-47.142857142857</v>
       </c>
       <c r="N18" s="14">
-        <v>-85.267857142857</v>
+        <v>-84.710743801652</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,13 +1057,13 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
+        <v>6</v>
+      </c>
+      <c r="D19" s="15">
         <v>7</v>
       </c>
-      <c r="D19" s="15">
-        <v>4</v>
-      </c>
       <c r="E19" s="14">
-        <v>75</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F19" s="15">
         <v>27</v>
@@ -1075,22 +1075,22 @@
         <v>-6.896551724137</v>
       </c>
       <c r="I19" s="15">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="J19" s="15">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="K19" s="14">
-        <v>-10</v>
+        <v>-9.278350515463</v>
       </c>
       <c r="L19" s="14">
-        <v>-27.027027027027</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="M19" s="14">
-        <v>15.714285714285</v>
+        <v>14.285714285714</v>
       </c>
       <c r="N19" s="14">
-        <v>-13.829787234042</v>
+        <v>-10.204081632653</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="15">
+        <v>1</v>
+      </c>
+      <c r="E20" s="14">
+        <v>0</v>
+      </c>
+      <c r="F20" s="15">
         <v>5</v>
       </c>
-      <c r="E20" s="14">
-        <v>-60</v>
-      </c>
-      <c r="F20" s="15">
-        <v>8</v>
-      </c>
       <c r="G20" s="15">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="H20" s="14">
-        <v>-61.904761904761</v>
+        <v>-50</v>
       </c>
       <c r="I20" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J20" s="15">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K20" s="14">
-        <v>-64.705882352941</v>
+        <v>-63.461538461538</v>
       </c>
       <c r="L20" s="14">
-        <v>-59.090909090909</v>
+        <v>-62</v>
       </c>
       <c r="M20" s="14">
-        <v>0</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="N20" s="14">
-        <v>-80.851063829787</v>
+        <v>-81.372549019607</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D21" s="17">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18">
-        <v>-44</v>
+        <v>-34.482758620689</v>
       </c>
       <c r="F21" s="17">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="G21" s="17">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H21" s="18">
-        <v>-35.514018691588</v>
+        <v>-39.622641509434</v>
       </c>
       <c r="I21" s="17">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="J21" s="17">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="K21" s="18">
-        <v>-28.116710875331</v>
+        <v>-28.325123152709</v>
       </c>
       <c r="L21" s="18">
-        <v>-35.167464114832</v>
+        <v>-35.044642857142</v>
       </c>
       <c r="M21" s="18">
-        <v>-20.294117647058</v>
+        <v>-20.491803278688</v>
       </c>
       <c r="N21" s="18">
-        <v>-63.962765957446</v>
+        <v>-64.206642066420</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1188,14 +1188,14 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="15">
-        <v>1</v>
-      </c>
-      <c r="G22" s="15">
-        <v>2</v>
-      </c>
-      <c r="H22" s="14">
-        <v>-50</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="15">
         <v>8</v>
@@ -1210,7 +1210,7 @@
         <v>14.285714285714</v>
       </c>
       <c r="M22" s="14">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="15">
+        <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1239,19 +1239,19 @@
         <v>21</v>
       </c>
       <c r="I23" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J23" s="15">
         <v>2</v>
       </c>
       <c r="K23" s="14">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L23" s="14">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="M23" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D24" s="15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E24" s="14">
-        <v>41.666666666666</v>
+        <v>50</v>
       </c>
       <c r="F24" s="15">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G24" s="15">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H24" s="14">
-        <v>3.174603174603</v>
+        <v>-4.6875</v>
       </c>
       <c r="I24" s="15">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="J24" s="15">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="K24" s="14">
-        <v>-23.505976095617</v>
+        <v>-21.072796934865</v>
       </c>
       <c r="L24" s="14">
-        <v>-8.571428571428</v>
+        <v>-3.738317757009</v>
       </c>
       <c r="M24" s="14">
-        <v>45.454545454545</v>
+        <v>43.055555555555</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D25" s="15">
         <v>1</v>
       </c>
       <c r="E25" s="14">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F25" s="15">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G25" s="15">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H25" s="14">
-        <v>15.384615384615</v>
+        <v>30</v>
       </c>
       <c r="I25" s="15">
         <v>46</v>
       </c>
       <c r="J25" s="15">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K25" s="14">
-        <v>-34.285714285714</v>
+        <v>-35.211267605633</v>
       </c>
       <c r="L25" s="14">
-        <v>-17.857142857142</v>
+        <v>-20.689655172413</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D26" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E26" s="14">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F26" s="15">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G26" s="15">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H26" s="14">
-        <v>-5.660377358490</v>
+        <v>0</v>
       </c>
       <c r="I26" s="15">
+        <v>191</v>
+      </c>
+      <c r="J26" s="15">
         <v>179</v>
       </c>
-      <c r="J26" s="15">
-        <v>170</v>
-      </c>
       <c r="K26" s="14">
-        <v>5.294117647058</v>
+        <v>6.703910614525</v>
       </c>
       <c r="L26" s="14">
-        <v>2.285714285714</v>
+        <v>3.243243243243</v>
       </c>
       <c r="M26" s="14">
-        <v>26.056338028169</v>
+        <v>24.836601307189</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,7 +1388,7 @@
         <v>20</v>
       </c>
       <c r="D27" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="14">
         <v>-100</v>
@@ -1406,10 +1406,10 @@
         <v>8</v>
       </c>
       <c r="J27" s="15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K27" s="14">
-        <v>-60</v>
+        <v>-61.904761904761</v>
       </c>
       <c r="L27" s="14">
         <v>-60</v>
@@ -1429,31 +1429,31 @@
         <v>20</v>
       </c>
       <c r="D28" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="14">
         <v>-100</v>
       </c>
       <c r="F28" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G28" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H28" s="14">
-        <v>-70</v>
+        <v>-88.888888888888</v>
       </c>
       <c r="I28" s="15">
         <v>4</v>
       </c>
       <c r="J28" s="15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K28" s="14">
-        <v>-85.714285714285</v>
+        <v>-86.206896551724</v>
       </c>
       <c r="L28" s="14">
-        <v>-86.206896551724</v>
+        <v>-87.878787878787</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1494,13 +1494,13 @@
         <v>21</v>
       </c>
       <c r="L29" s="14">
-        <v>-83.333333333333</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="M29" s="14">
         <v>-80</v>
       </c>
       <c r="N29" s="14">
-        <v>-95.454545454545</v>
+        <v>-95.652173913043</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1535,13 +1535,13 @@
         <v>21</v>
       </c>
       <c r="L30" s="14">
-        <v>-80</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="M30" s="14">
         <v>-80</v>
       </c>
       <c r="N30" s="14">
-        <v>-95.238095238095</v>
+        <v>-95.454545454545</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1610,29 +1610,29 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="15">
+        <v>1</v>
+      </c>
+      <c r="E33" s="14">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>21</v>
+      <c r="G33" s="15">
+        <v>1</v>
+      </c>
+      <c r="H33" s="14">
+        <v>-100</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" s="13" t="s">
-        <v>21</v>
+      <c r="J33" s="15">
+        <v>1</v>
+      </c>
+      <c r="K33" s="14">
+        <v>-100</v>
       </c>
       <c r="L33" s="14">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-041pct.xlsx
+++ b/data/source/weekly/cs-en-us-041pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -895,17 +895,17 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="14">
         <v>-100</v>
@@ -926,7 +926,7 @@
         <v>33.333333333333</v>
       </c>
       <c r="N15" s="14">
-        <v>0</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E16" s="14">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G16" s="15">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H16" s="14">
-        <v>-62.5</v>
+        <v>-61.904761904761</v>
       </c>
       <c r="I16" s="15">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J16" s="15">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="K16" s="14">
-        <v>-11.111111111111</v>
+        <v>-16.129032258064</v>
       </c>
       <c r="L16" s="14">
-        <v>-39.240506329113</v>
+        <v>-40.229885057471</v>
       </c>
       <c r="M16" s="14">
-        <v>-31.428571428571</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="N16" s="14">
-        <v>-79.661016949152</v>
+        <v>-79.766536964980</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" s="15">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E17" s="14">
-        <v>-54.545454545454</v>
+        <v>-25</v>
       </c>
       <c r="F17" s="15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G17" s="15">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H17" s="14">
-        <v>-42.424242424242</v>
+        <v>-37.5</v>
       </c>
       <c r="I17" s="15">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="J17" s="15">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="K17" s="14">
-        <v>-32.592592592592</v>
+        <v>-32.167832167832</v>
       </c>
       <c r="L17" s="14">
-        <v>-30.534351145038</v>
+        <v>-29.197080291970</v>
       </c>
       <c r="M17" s="14">
-        <v>-25.409836065573</v>
+        <v>-22.4</v>
       </c>
       <c r="N17" s="14">
-        <v>-22.222222222222</v>
+        <v>-24.806201550387</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E18" s="14">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F18" s="15">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G18" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H18" s="14">
-        <v>-53.333333333333</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="I18" s="15">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J18" s="15">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="K18" s="14">
-        <v>-35.087719298245</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L18" s="14">
-        <v>-33.928571428571</v>
+        <v>-28.813559322033</v>
       </c>
       <c r="M18" s="14">
-        <v>-47.142857142857</v>
+        <v>-44</v>
       </c>
       <c r="N18" s="14">
-        <v>-84.710743801652</v>
+        <v>-84.090909090909</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D19" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E19" s="14">
-        <v>-14.285714285714</v>
+        <v>120</v>
       </c>
       <c r="F19" s="15">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G19" s="15">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H19" s="14">
-        <v>-6.896551724137</v>
+        <v>28</v>
       </c>
       <c r="I19" s="15">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="J19" s="15">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="K19" s="14">
-        <v>-9.278350515463</v>
+        <v>-2.941176470588</v>
       </c>
       <c r="L19" s="14">
-        <v>-27.272727272727</v>
+        <v>-22.047244094488</v>
       </c>
       <c r="M19" s="14">
-        <v>14.285714285714</v>
+        <v>23.75</v>
       </c>
       <c r="N19" s="14">
-        <v>-10.204081632653</v>
+        <v>-7.476635514018</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" s="15">
         <v>1</v>
       </c>
       <c r="E20" s="14">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F20" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G20" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H20" s="14">
-        <v>-50</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I20" s="15">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J20" s="15">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K20" s="14">
-        <v>-63.461538461538</v>
+        <v>-58.490566037735</v>
       </c>
       <c r="L20" s="14">
-        <v>-62</v>
+        <v>-63.333333333333</v>
       </c>
       <c r="M20" s="14">
-        <v>-9.523809523809</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="N20" s="14">
-        <v>-81.372549019607</v>
+        <v>-81.355932203389</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D21" s="17">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E21" s="18">
-        <v>-34.482758620689</v>
+        <v>3.571428571428</v>
       </c>
       <c r="F21" s="17">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="G21" s="17">
         <v>106</v>
       </c>
       <c r="H21" s="18">
-        <v>-39.622641509434</v>
+        <v>-25.471698113207</v>
       </c>
       <c r="I21" s="17">
-        <v>291</v>
+        <v>320</v>
       </c>
       <c r="J21" s="17">
-        <v>406</v>
+        <v>434</v>
       </c>
       <c r="K21" s="18">
-        <v>-28.325123152709</v>
+        <v>-26.267281105990</v>
       </c>
       <c r="L21" s="18">
-        <v>-35.044642857142</v>
+        <v>-33.471933471933</v>
       </c>
       <c r="M21" s="18">
-        <v>-20.491803278688</v>
+        <v>-16.883116883116</v>
       </c>
       <c r="N21" s="18">
-        <v>-64.206642066420</v>
+        <v>-64.245810055865</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="15">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1188,8 +1188,8 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+      <c r="F22" s="15">
+        <v>1</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,19 +1198,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J22" s="15">
         <v>7</v>
       </c>
       <c r="K22" s="14">
-        <v>14.285714285714</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L22" s="14">
-        <v>14.285714285714</v>
+        <v>12.5</v>
       </c>
       <c r="M22" s="14">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D24" s="15">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E24" s="14">
-        <v>50</v>
+        <v>-35</v>
       </c>
       <c r="F24" s="15">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G24" s="15">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H24" s="14">
-        <v>-4.6875</v>
+        <v>-10.769230769230</v>
       </c>
       <c r="I24" s="15">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="J24" s="15">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="K24" s="14">
-        <v>-21.072796934865</v>
+        <v>-22.064056939501</v>
       </c>
       <c r="L24" s="14">
-        <v>-3.738317757009</v>
+        <v>-9.876543209876</v>
       </c>
       <c r="M24" s="14">
-        <v>43.055555555555</v>
+        <v>43.137254901960</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D25" s="15">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E25" s="14">
-        <v>0</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F25" s="15">
         <v>13</v>
       </c>
       <c r="G25" s="15">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H25" s="14">
-        <v>30</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="I25" s="15">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J25" s="15">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="K25" s="14">
-        <v>-35.211267605633</v>
+        <v>-35.897435897435</v>
       </c>
       <c r="L25" s="14">
-        <v>-20.689655172413</v>
+        <v>-21.875</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D26" s="15">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E26" s="14">
-        <v>33.333333333333</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="F26" s="15">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G26" s="15">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H26" s="14">
-        <v>0</v>
+        <v>15.094339622641</v>
       </c>
       <c r="I26" s="15">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="J26" s="15">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="K26" s="14">
-        <v>6.703910614525</v>
+        <v>5.583756345177</v>
       </c>
       <c r="L26" s="14">
-        <v>3.243243243243</v>
+        <v>8.333333333333</v>
       </c>
       <c r="M26" s="14">
-        <v>24.836601307189</v>
+        <v>24.550898203592</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="15">
+      <c r="C27" s="15">
         <v>1</v>
       </c>
-      <c r="E27" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="15">
+        <v>1</v>
       </c>
       <c r="G27" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H27" s="14">
-        <v>-100</v>
+        <v>-80</v>
       </c>
       <c r="I27" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J27" s="15">
         <v>21</v>
       </c>
       <c r="K27" s="14">
-        <v>-61.904761904761</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L27" s="14">
-        <v>-60</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>20</v>
       </c>
       <c r="D28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="14">
         <v>-100</v>
       </c>
-      <c r="F28" s="15">
-        <v>1</v>
+      <c r="F28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G28" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H28" s="14">
-        <v>-88.888888888888</v>
+        <v>-100</v>
       </c>
       <c r="I28" s="15">
         <v>4</v>
       </c>
       <c r="J28" s="15">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K28" s="14">
-        <v>-86.206896551724</v>
+        <v>-87.096774193548</v>
       </c>
       <c r="L28" s="14">
-        <v>-87.878787878787</v>
+        <v>-89.189189189189</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="15">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="15">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1485,7 +1485,7 @@
         <v>21</v>
       </c>
       <c r="I29" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>20</v>
@@ -1494,21 +1494,21 @@
         <v>21</v>
       </c>
       <c r="L29" s="14">
-        <v>-85.714285714285</v>
+        <v>-75</v>
       </c>
       <c r="M29" s="14">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="N29" s="14">
-        <v>-95.652173913043</v>
+        <v>-91.666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="15">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="15">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1526,7 +1526,7 @@
         <v>21</v>
       </c>
       <c r="I30" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>20</v>
@@ -1535,13 +1535,13 @@
         <v>21</v>
       </c>
       <c r="L30" s="14">
-        <v>-83.333333333333</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="M30" s="14">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="N30" s="14">
-        <v>-95.454545454545</v>
+        <v>-91.304347826087</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1610,11 +1610,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="15">
-        <v>1</v>
-      </c>
-      <c r="E33" s="14">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-041pct.xlsx
+++ b/data/source/weekly/cs-en-us-041pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -905,7 +905,7 @@
         <v>20</v>
       </c>
       <c r="G15" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="14">
         <v>-100</v>
@@ -920,13 +920,13 @@
         <v>-27.272727272727</v>
       </c>
       <c r="L15" s="14">
-        <v>-11.111111111111</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="M15" s="14">
         <v>33.333333333333</v>
       </c>
       <c r="N15" s="14">
-        <v>-20</v>
+        <v>-27.272727272727</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
+        <v>2</v>
+      </c>
+      <c r="D16" s="15">
         <v>4</v>
-      </c>
-      <c r="D16" s="15">
-        <v>8</v>
       </c>
       <c r="E16" s="14">
         <v>-50</v>
       </c>
       <c r="F16" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G16" s="15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H16" s="14">
-        <v>-61.904761904761</v>
+        <v>-50</v>
       </c>
       <c r="I16" s="15">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J16" s="15">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K16" s="14">
-        <v>-16.129032258064</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L16" s="14">
-        <v>-40.229885057471</v>
+        <v>-41.304347826087</v>
       </c>
       <c r="M16" s="14">
-        <v>-31.578947368421</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N16" s="14">
-        <v>-79.766536964980</v>
+        <v>-80.219780219780</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
+        <v>12</v>
+      </c>
+      <c r="D17" s="15">
         <v>6</v>
       </c>
-      <c r="D17" s="15">
-        <v>8</v>
-      </c>
       <c r="E17" s="14">
-        <v>-25</v>
+        <v>100</v>
       </c>
       <c r="F17" s="15">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G17" s="15">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H17" s="14">
-        <v>-37.5</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I17" s="15">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="J17" s="15">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="K17" s="14">
-        <v>-32.167832167832</v>
+        <v>-26.174496644295</v>
       </c>
       <c r="L17" s="14">
-        <v>-29.197080291970</v>
+        <v>-22.535211267605</v>
       </c>
       <c r="M17" s="14">
-        <v>-22.4</v>
+        <v>-16.030534351145</v>
       </c>
       <c r="N17" s="14">
-        <v>-24.806201550387</v>
+        <v>-19.117647058823</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D18" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>-16.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F18" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G18" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H18" s="14">
-        <v>-29.411764705882</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I18" s="15">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J18" s="15">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K18" s="14">
-        <v>-33.333333333333</v>
+        <v>-30.303030303030</v>
       </c>
       <c r="L18" s="14">
-        <v>-28.813559322033</v>
+        <v>-26.984126984127</v>
       </c>
       <c r="M18" s="14">
-        <v>-44</v>
+        <v>-41.772151898734</v>
       </c>
       <c r="N18" s="14">
-        <v>-84.090909090909</v>
+        <v>-83.916083916083</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D19" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E19" s="14">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="F19" s="15">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G19" s="15">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H19" s="14">
-        <v>28</v>
+        <v>41.666666666666</v>
       </c>
       <c r="I19" s="15">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="J19" s="15">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="K19" s="14">
-        <v>-2.941176470588</v>
+        <v>-0.909090909090</v>
       </c>
       <c r="L19" s="14">
-        <v>-22.047244094488</v>
+        <v>-19.259259259259</v>
       </c>
       <c r="M19" s="14">
-        <v>23.75</v>
+        <v>28.235294117647</v>
       </c>
       <c r="N19" s="14">
-        <v>-7.476635514018</v>
+        <v>-9.166666666666</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>3</v>
       </c>
       <c r="D20" s="15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E20" s="14">
-        <v>200</v>
+        <v>-40</v>
       </c>
       <c r="F20" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G20" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H20" s="14">
-        <v>-22.222222222222</v>
+        <v>-25</v>
       </c>
       <c r="I20" s="15">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J20" s="15">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K20" s="14">
-        <v>-58.490566037735</v>
+        <v>-56.896551724137</v>
       </c>
       <c r="L20" s="14">
-        <v>-63.333333333333</v>
+        <v>-59.016393442622</v>
       </c>
       <c r="M20" s="14">
-        <v>-4.347826086956</v>
+        <v>0</v>
       </c>
       <c r="N20" s="14">
-        <v>-81.355932203389</v>
+        <v>-80.314960629921</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D21" s="17">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E21" s="18">
-        <v>3.571428571428</v>
+        <v>19.230769230769</v>
       </c>
       <c r="F21" s="17">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="G21" s="17">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H21" s="18">
-        <v>-25.471698113207</v>
+        <v>-12.962962962963</v>
       </c>
       <c r="I21" s="17">
-        <v>320</v>
+        <v>352</v>
       </c>
       <c r="J21" s="17">
-        <v>434</v>
+        <v>460</v>
       </c>
       <c r="K21" s="18">
-        <v>-26.267281105990</v>
+        <v>-23.478260869565</v>
       </c>
       <c r="L21" s="18">
-        <v>-33.471933471933</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="M21" s="18">
-        <v>-16.883116883116</v>
+        <v>-13.513513513513</v>
       </c>
       <c r="N21" s="18">
-        <v>-64.245810055865</v>
+        <v>-63.447559709242</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,7 +1180,7 @@
         <v>29</v>
       </c>
       <c r="C22" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,19 +1198,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J22" s="15">
         <v>7</v>
       </c>
       <c r="K22" s="14">
-        <v>28.571428571428</v>
+        <v>71.428571428571</v>
       </c>
       <c r="L22" s="14">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="M22" s="14">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1230,7 +1230,7 @@
         <v>21</v>
       </c>
       <c r="F23" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>20</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D24" s="15">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E24" s="14">
-        <v>-35</v>
+        <v>70</v>
       </c>
       <c r="F24" s="15">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G24" s="15">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="H24" s="14">
-        <v>-10.769230769230</v>
+        <v>19.230769230769</v>
       </c>
       <c r="I24" s="15">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="J24" s="15">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="K24" s="14">
-        <v>-22.064056939501</v>
+        <v>-18.900343642611</v>
       </c>
       <c r="L24" s="14">
-        <v>-9.876543209876</v>
+        <v>-5.976095617529</v>
       </c>
       <c r="M24" s="14">
-        <v>43.137254901960</v>
+        <v>44.785276073619</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D25" s="15">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E25" s="14">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G25" s="15">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H25" s="14">
-        <v>-7.142857142857</v>
+        <v>9.090909090909</v>
       </c>
       <c r="I25" s="15">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J25" s="15">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K25" s="14">
-        <v>-35.897435897435</v>
+        <v>-36.25</v>
       </c>
       <c r="L25" s="14">
-        <v>-21.875</v>
+        <v>-23.880597014925</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D26" s="15">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E26" s="14">
-        <v>-5.555555555555</v>
+        <v>100</v>
       </c>
       <c r="F26" s="15">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G26" s="15">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="H26" s="14">
-        <v>15.094339622641</v>
+        <v>31.111111111111</v>
       </c>
       <c r="I26" s="15">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="J26" s="15">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="K26" s="14">
-        <v>5.583756345177</v>
+        <v>8.780487804878</v>
       </c>
       <c r="L26" s="14">
-        <v>8.333333333333</v>
+        <v>7.729468599033</v>
       </c>
       <c r="M26" s="14">
-        <v>24.550898203592</v>
+        <v>21.857923497267</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1397,10 +1397,10 @@
         <v>1</v>
       </c>
       <c r="G27" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H27" s="14">
-        <v>-80</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I27" s="15">
         <v>9</v>
@@ -1412,7 +1412,7 @@
         <v>-57.142857142857</v>
       </c>
       <c r="L27" s="14">
-        <v>-57.142857142857</v>
+        <v>-62.5</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,7 +1429,7 @@
         <v>20</v>
       </c>
       <c r="D28" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="14">
         <v>-100</v>
@@ -1438,7 +1438,7 @@
         <v>20</v>
       </c>
       <c r="G28" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H28" s="14">
         <v>-100</v>
@@ -1447,13 +1447,13 @@
         <v>4</v>
       </c>
       <c r="J28" s="15">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K28" s="14">
-        <v>-87.096774193548</v>
+        <v>-88.235294117647</v>
       </c>
       <c r="L28" s="14">
-        <v>-89.189189189189</v>
+        <v>-89.743589743589</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="15">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1497,7 +1497,7 @@
         <v>-75</v>
       </c>
       <c r="M29" s="14">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N29" s="14">
         <v>-91.666666666666</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="15">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1538,7 +1538,7 @@
         <v>-71.428571428571</v>
       </c>
       <c r="M30" s="14">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N30" s="14">
         <v>-91.304347826087</v>

--- a/data/source/weekly/cs-en-us-041pct.xlsx
+++ b/data/source/weekly/cs-en-us-041pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -895,17 +895,17 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>2</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H15" s="14">
         <v>-100</v>
@@ -914,19 +914,19 @@
         <v>8</v>
       </c>
       <c r="J15" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K15" s="14">
-        <v>-27.272727272727</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="L15" s="14">
-        <v>-27.272727272727</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M15" s="14">
         <v>33.333333333333</v>
       </c>
       <c r="N15" s="14">
-        <v>-27.272727272727</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" s="15">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E16" s="14">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="F16" s="15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G16" s="15">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="H16" s="14">
-        <v>-50</v>
+        <v>-51.851851851851</v>
       </c>
       <c r="I16" s="15">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J16" s="15">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="K16" s="14">
-        <v>-18.181818181818</v>
+        <v>-23.684210526315</v>
       </c>
       <c r="L16" s="14">
-        <v>-41.304347826087</v>
+        <v>-39.583333333333</v>
       </c>
       <c r="M16" s="14">
         <v>-33.333333333333</v>
       </c>
       <c r="N16" s="14">
-        <v>-80.219780219780</v>
+        <v>-79.861111111111</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D17" s="15">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E17" s="14">
-        <v>100</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="F17" s="15">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G17" s="15">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H17" s="14">
-        <v>-18.181818181818</v>
+        <v>-19.444444444444</v>
       </c>
       <c r="I17" s="15">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="J17" s="15">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="K17" s="14">
-        <v>-26.174496644295</v>
+        <v>-27.5</v>
       </c>
       <c r="L17" s="14">
-        <v>-22.535211267605</v>
+        <v>-21.088435374149</v>
       </c>
       <c r="M17" s="14">
-        <v>-16.030534351145</v>
+        <v>-18.309859154929</v>
       </c>
       <c r="N17" s="14">
-        <v>-19.117647058823</v>
+        <v>-21.088435374149</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>4</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E18" s="14">
-        <v>33.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="15">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G18" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H18" s="14">
-        <v>-22.222222222222</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="I18" s="15">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J18" s="15">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K18" s="14">
-        <v>-30.303030303030</v>
+        <v>-30.555555555555</v>
       </c>
       <c r="L18" s="14">
-        <v>-26.984126984127</v>
+        <v>-25.373134328358</v>
       </c>
       <c r="M18" s="14">
-        <v>-41.772151898734</v>
+        <v>-39.024390243902</v>
       </c>
       <c r="N18" s="14">
-        <v>-83.916083916083</v>
+        <v>-83.660130718954</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D19" s="15">
         <v>8</v>
       </c>
       <c r="E19" s="14">
-        <v>25</v>
+        <v>-37.5</v>
       </c>
       <c r="F19" s="15">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G19" s="15">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H19" s="14">
-        <v>41.666666666666</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I19" s="15">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="J19" s="15">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="K19" s="14">
-        <v>-0.909090909090</v>
+        <v>-0.847457627118</v>
       </c>
       <c r="L19" s="14">
-        <v>-19.259259259259</v>
+        <v>-22</v>
       </c>
       <c r="M19" s="14">
-        <v>28.235294117647</v>
+        <v>32.954545454545</v>
       </c>
       <c r="N19" s="14">
-        <v>-9.166666666666</v>
+        <v>-11.363636363636</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>3</v>
       </c>
       <c r="D20" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E20" s="14">
-        <v>-40</v>
+        <v>-25</v>
       </c>
       <c r="F20" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G20" s="15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H20" s="14">
-        <v>-25</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I20" s="15">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J20" s="15">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K20" s="14">
-        <v>-56.896551724137</v>
+        <v>-56.451612903225</v>
       </c>
       <c r="L20" s="14">
-        <v>-59.016393442622</v>
+        <v>-57.8125</v>
       </c>
       <c r="M20" s="14">
         <v>0</v>
       </c>
       <c r="N20" s="14">
-        <v>-80.314960629921</v>
+        <v>-80.147058823529</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D21" s="17">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="E21" s="18">
-        <v>19.230769230769</v>
+        <v>-46.341463414634</v>
       </c>
       <c r="F21" s="17">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G21" s="17">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="H21" s="18">
+        <v>-18.548387096774</v>
+      </c>
+      <c r="I21" s="17">
+        <v>376</v>
+      </c>
+      <c r="J21" s="17">
+        <v>501</v>
+      </c>
+      <c r="K21" s="18">
+        <v>-24.950099800399</v>
+      </c>
+      <c r="L21" s="18">
+        <v>-30.370370370370</v>
+      </c>
+      <c r="M21" s="18">
         <v>-12.962962962963</v>
       </c>
-      <c r="I21" s="17">
-        <v>352</v>
-      </c>
-      <c r="J21" s="17">
-        <v>460</v>
-      </c>
-      <c r="K21" s="18">
-        <v>-23.478260869565</v>
-      </c>
-      <c r="L21" s="18">
-        <v>-30.434782608695</v>
-      </c>
-      <c r="M21" s="18">
-        <v>-13.513513513513</v>
-      </c>
       <c r="N21" s="18">
-        <v>-63.447559709242</v>
+        <v>-63.565891472868</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>3</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1210,7 +1210,7 @@
         <v>50</v>
       </c>
       <c r="M22" s="14">
-        <v>100</v>
+        <v>71.428571428571</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1248,10 +1248,10 @@
         <v>100</v>
       </c>
       <c r="L23" s="14">
-        <v>-60</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="M23" s="14">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D24" s="15">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E24" s="14">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F24" s="15">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G24" s="15">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H24" s="14">
-        <v>19.230769230769</v>
+        <v>9.090909090909</v>
       </c>
       <c r="I24" s="15">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="J24" s="15">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="K24" s="14">
-        <v>-18.900343642611</v>
+        <v>-17.973856209150</v>
       </c>
       <c r="L24" s="14">
-        <v>-5.976095617529</v>
+        <v>-6.343283582089</v>
       </c>
       <c r="M24" s="14">
-        <v>44.785276073619</v>
+        <v>36.413043478260</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="15">
         <v>2</v>
       </c>
       <c r="E25" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F25" s="15">
+        <v>8</v>
+      </c>
+      <c r="G25" s="15">
         <v>12</v>
       </c>
-      <c r="G25" s="15">
-        <v>11</v>
-      </c>
       <c r="H25" s="14">
-        <v>9.090909090909</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I25" s="15">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J25" s="15">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K25" s="14">
-        <v>-36.25</v>
+        <v>-35.365853658536</v>
       </c>
       <c r="L25" s="14">
-        <v>-23.880597014925</v>
+        <v>-24.285714285714</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D26" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E26" s="14">
-        <v>100</v>
+        <v>88.888888888888</v>
       </c>
       <c r="F26" s="15">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G26" s="15">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H26" s="14">
-        <v>31.111111111111</v>
+        <v>40.909090909090</v>
       </c>
       <c r="I26" s="15">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="J26" s="15">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="K26" s="14">
-        <v>8.780487804878</v>
+        <v>12.149532710280</v>
       </c>
       <c r="L26" s="14">
-        <v>7.729468599033</v>
+        <v>6.666666666666</v>
       </c>
       <c r="M26" s="14">
-        <v>21.857923497267</v>
+        <v>23.076923076923</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="15">
+        <v>3</v>
+      </c>
+      <c r="E27" s="14">
+        <v>-100</v>
       </c>
       <c r="F27" s="15">
         <v>1</v>
       </c>
       <c r="G27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="I27" s="15">
         <v>9</v>
       </c>
       <c r="J27" s="15">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K27" s="14">
-        <v>-57.142857142857</v>
+        <v>-62.5</v>
       </c>
       <c r="L27" s="14">
-        <v>-62.5</v>
+        <v>-67.857142857142</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="15">
-        <v>3</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="15">
+        <v>4</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="15">
+        <v>4</v>
       </c>
       <c r="G28" s="15">
+        <v>6</v>
+      </c>
+      <c r="H28" s="14">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="I28" s="15">
         <v>8</v>
-      </c>
-      <c r="H28" s="14">
-        <v>-100</v>
-      </c>
-      <c r="I28" s="15">
-        <v>4</v>
       </c>
       <c r="J28" s="15">
         <v>34</v>
       </c>
       <c r="K28" s="14">
-        <v>-88.235294117647</v>
+        <v>-76.470588235294</v>
       </c>
       <c r="L28" s="14">
-        <v>-89.743589743589</v>
+        <v>-80.952380952380</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,29 +1469,29 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="15">
+        <v>1</v>
+      </c>
+      <c r="E29" s="14">
+        <v>-100</v>
       </c>
       <c r="F29" s="15">
         <v>1</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="15">
+        <v>1</v>
+      </c>
+      <c r="H29" s="14">
+        <v>0</v>
       </c>
       <c r="I29" s="15">
         <v>2</v>
       </c>
-      <c r="J29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K29" s="13" t="s">
-        <v>21</v>
+      <c r="J29" s="15">
+        <v>1</v>
+      </c>
+      <c r="K29" s="14">
+        <v>100</v>
       </c>
       <c r="L29" s="14">
         <v>-75</v>
@@ -1500,7 +1500,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N29" s="14">
-        <v>-91.666666666666</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,29 +1510,29 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="15">
+        <v>1</v>
+      </c>
+      <c r="E30" s="14">
+        <v>-100</v>
       </c>
       <c r="F30" s="15">
         <v>1</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="15">
+        <v>1</v>
+      </c>
+      <c r="H30" s="14">
+        <v>0</v>
       </c>
       <c r="I30" s="15">
         <v>2</v>
       </c>
-      <c r="J30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K30" s="13" t="s">
-        <v>21</v>
+      <c r="J30" s="15">
+        <v>1</v>
+      </c>
+      <c r="K30" s="14">
+        <v>100</v>
       </c>
       <c r="L30" s="14">
         <v>-71.428571428571</v>
@@ -1541,7 +1541,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N30" s="14">
-        <v>-91.304347826087</v>
+        <v>-92</v>
       </c>
     </row>
     <row r="31" spans="1:14">
